--- a/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
+++ b/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
@@ -4133,7 +4133,7 @@
     <row r="390" ht="15.75" customHeight="1" s="4">
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>FUNDACAO - ANFITEATRO VARGAS FURTADO</t>
+          <t>FUNDACAO - ANFITEATRO JARBAS FURTADO</t>
         </is>
       </c>
       <c r="E390" s="3" t="n">

--- a/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
+++ b/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
@@ -341,7 +341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E412"/>
+  <dimension ref="A1:E429"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="52" customWidth="1" style="4" min="1" max="1"/>
@@ -614,3760 +614,3910 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="4">
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>SALA DA DIRETORIA DE ENSINO</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>20022</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PREDIO CENTRAL - SALA DE TELECOM</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20023</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="4">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>COORDENACAO GERAL DE ENSINO TECNICO</t>
+          <t>SALA DA DIRETORIA DE ENSINO</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>21000</v>
+        <v>20022</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="4">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>COORDENACAO GERAL DE GRADUACAO</t>
+          <t>COORDENACAO GERAL DE ENSINO TECNICO</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>22000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="4">
       <c r="B29" s="3" t="inlineStr">
         <is>
+          <t>COORDENACAO GERAL DE GRADUACAO</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="4">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
           <t>COORDENACAO GERAL DE ASSUNTOS E REGISTROS ACADEMIC</t>
         </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="4">
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>COORDENACAO GERAL DE ASSUNTOS E REGISTROS ACADEMIC</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>23000</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="4">
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>SECRETARIA DE REGISTROS ESCOLARES - TÉCNICO</t>
+          <t>COORDENACAO GERAL DE ASSUNTOS E REGISTROS ACADEMIC</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>23100</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="4">
       <c r="C32" s="3" t="inlineStr">
         <is>
+          <t>SECRETARIA DE REGISTROS ESCOLARES - TÉCNICO</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>23100</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="4">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
           <t>SECRETARIA DE REGISTROS ESCOLARES - GRADUAÇÃO</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>23200</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" s="4">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>COORDENACAO GERAL DE ASSISTENCIA ESTUDANTIL</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>24000</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="4">
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ENFERMARIA - SERVICO MEDICO E ODONTOLOGICO</t>
+          <t>COORDENACAO GERAL DE ASSISTENCIA ESTUDANTIL</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>24100</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="4">
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>NAI - NUCLEO DE ACOES INCLUSIVAS</t>
+          <t>ENFERMARIA - SERVICO MEDICO E ODONTOLOGICO</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>24200</v>
+        <v>24100</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="4">
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t>NAI - NUCLEO DE ACOES INCLUSIVAS</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="4">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t>REFEITORIO</t>
         </is>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" s="4">
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>REFEITORIO</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>24300</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="4">
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>COZINHA</t>
+          <t>REFEITORIO</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>24301</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="4">
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>SALA NUTRICIONISTAS</t>
+          <t>COZINHA</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>24302</v>
+        <v>24301</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="4">
       <c r="C40" s="3" t="inlineStr">
         <is>
+          <t>SALA NUTRICIONISTAS</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>24302</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="4">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
           <t>REFEITORIO - AREA DE ALIMENTACAO</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>24303</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="4">
-      <c r="B41" s="3" t="inlineStr">
+    <row r="42" ht="15.75" customHeight="1" s="4">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>BIBLIOTECA</t>
         </is>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" s="4">
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>BIBLIOTECA</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>25000</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="4">
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>BIBLIOTECA - PRIMEIRO ANDAR</t>
+          <t>BIBLIOTECA</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>25001</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="4">
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>BIBLIOTECA - PRIMEIRO ANDAR - DEPOSITO</t>
+          <t>BIBLIOTECA - PRIMEIRO ANDAR</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>25002</v>
+        <v>25001</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="4">
       <c r="C45" s="3" t="inlineStr">
         <is>
+          <t>BIBLIOTECA - PRIMEIRO ANDAR - DEPOSITO</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>25002</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="4">
+      <c r="C46" s="3" t="inlineStr">
+        <is>
           <t>BIBLIOTECA - SEGUNDO ANDAR</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>25003</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="4">
-      <c r="B46" s="3" t="inlineStr">
+    <row r="47" ht="15.75" customHeight="1" s="4">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>CEAD - COORDENACAO DE ENSINO A DISTANCIA</t>
         </is>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" s="4">
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>CEAD - COORDENACAO DE ENSINO A DISTANCIA</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>27000</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="4">
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>CEAD - LABORATORIO DE INFORMATICA 1</t>
+          <t>CEAD - COORDENACAO DE ENSINO A DISTANCIA</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>27001</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="4">
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>CEAD - LABORATORIO DE INFORMATICA 2</t>
+          <t>CEAD - LABORATORIO DE INFORMATICA 1</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>27002</v>
+        <v>27001</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="4">
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>CEAD - SALA DA COORDENACAO</t>
+          <t>CEAD - LABORATORIO DE INFORMATICA 2</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>27003</v>
+        <v>27002</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="4">
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>CEAD - SALA DOS PROFESSORES</t>
+          <t>CEAD - SALA DA COORDENACAO</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>27004</v>
+        <v>27003</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="4">
       <c r="C52" s="3" t="inlineStr">
         <is>
+          <t>CEAD - SALA DOS PROFESSORES</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>27004</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" s="4">
+      <c r="C53" s="3" t="inlineStr">
+        <is>
           <t>CEAD - ALMOXARIFADO</t>
         </is>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>27005</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="4">
-      <c r="B53" s="3" t="inlineStr">
+    <row r="54" ht="15.75" customHeight="1" s="4">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>IPCA - INSTITUTO DE PESQUISA E CIÊNCIAS APLICADAS</t>
         </is>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1" s="4">
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>IPCA - INSTITUTO DE PESQUISA E CIÊNCIAS APLICADAS</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>28000</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="4">
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 1º ANDAR - LABORATORIO DE BIOLOGIA VEGETAL</t>
+          <t>IPCA - INSTITUTO DE PESQUISA E CIÊNCIAS APLICADAS</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>28001</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="4">
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 1º ANDAR - LABORATORIO DE BIOQUIMICA E QUIMICA ORGANICA</t>
+          <t>IPCA - 1º ANDAR - LABORATORIO DE BIOLOGIA VEGETAL</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>28002</v>
+        <v>28001</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="4">
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 1º ANDAR - LABORATORIO DE ANALISE DE ALIMENTOS</t>
+          <t>IPCA - 1º ANDAR - LABORATORIO DE BIOQUIMICA E QUIMICA ORGANICA</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>28003</v>
+        <v>28002</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="4">
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 1º ANDAR - LABORATORIO DE NUTRICAO</t>
+          <t>IPCA - 1º ANDAR - LABORATORIO DE ANALISE DE ALIMENTOS</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>28004</v>
+        <v>28003</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="4">
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 1º ANDAR - LABORATORIO DE AGUA E RESIDUOS</t>
+          <t>IPCA - 1º ANDAR - LABORATORIO DE NUTRICAO</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>28005</v>
+        <v>28004</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="4">
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 1º ANDAR - LABORATORIO DE BIOLOGIA MOLECULAR E MICROORGANISMOS</t>
+          <t>IPCA - 1º ANDAR - LABORATORIO DE AGUA E RESIDUOS</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>28006</v>
+        <v>28005</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="4">
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 1º ANDAR - LABORATORIO DE QUIMICA AVANCADA</t>
+          <t>IPCA - 1º ANDAR - LABORATORIO DE BIOLOGIA MOLECULAR E MICROORGANISMOS</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>28007</v>
+        <v>28006</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="4">
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 1º ANDAR - DML</t>
+          <t>IPCA - 1º ANDAR - LABORATORIO DE QUIMICA AVANCADA</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>28008</v>
+        <v>28007</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="4">
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - LABORATORIO DE EQUIPAMENTOS ESPECIAIS</t>
+          <t>IPCA - 1º ANDAR - DML</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>28009</v>
+        <v>28008</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="4">
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2 ANDAR - NITTEC - EMBRAPII</t>
+          <t>IPCA - 2º ANDAR - LABORATORIO DE EQUIPAMENTOS ESPECIAIS</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>28010</v>
+        <v>28009</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="4">
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - LABORATORIO DE TV DIGITAL E VÍDEO</t>
+          <t>IPCA - 2 ANDAR - NITTEC - EMBRAPII</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>28011</v>
+        <v>28010</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="4">
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - LABORATORIO DE EDUCACAO APLICADA A NOVAS TECNOLOGIAS</t>
+          <t>IPCA - 2º ANDAR - LABORATORIO DE TV DIGITAL E VÍDEO</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>28012</v>
+        <v>28011</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="4">
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - PURIFICACAO DE AGUA  E PRODUCAO DE GELO</t>
+          <t>IPCA - 2º ANDAR - LABORATORIO DE EDUCACAO APLICADA A NOVAS TECNOLOGIAS</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>28013</v>
+        <v>28012</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="4">
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - ALMOXARIFADO DE REAGENTES</t>
+          <t>IPCA - 2º ANDAR - PURIFICACAO DE AGUA  E PRODUCAO DE GELO</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>28014</v>
+        <v>28013</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="4">
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - LABORATORIO DE ESTATISTICA</t>
+          <t>IPCA - 2º ANDAR - ALMOXARIFADO DE REAGENTES</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>28015</v>
+        <v>28014</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="4">
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - LABORATORIO DE GEOPROCESSAMENTO</t>
+          <t>IPCA - 2º ANDAR - LABORATORIO DE ESTATISTICA</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>28016</v>
+        <v>28015</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="4">
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - LABORATORIO DE SEGURANCA DO TRABALHO</t>
+          <t>IPCA - 2º ANDAR - LABORATORIO DE GEOPROCESSAMENTO</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>28017</v>
+        <v>28016</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="4">
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>IPCA - 2º ANDAR - SALA DE REUNIAO</t>
+          <t>IPCA - 2º ANDAR - LABORATORIO DE SEGURANCA DO TRABALHO</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>28018</v>
+        <v>28017</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="4">
       <c r="C73" s="3" t="inlineStr">
         <is>
+          <t>IPCA - 2º ANDAR - SALA DE REUNIAO</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>28018</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" s="4">
+      <c r="C74" s="3" t="inlineStr">
+        <is>
           <t>IPCA - 2º ANDAR - COPA</t>
         </is>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E74" s="3" t="n">
         <v>28019</v>
       </c>
     </row>
-    <row r="74" ht="15.75" customHeight="1" s="4">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="75" ht="15.75" customHeight="1" s="4">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" s="4">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTOS</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="4">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>DAAA - DEP. ACADEM. DE AGRICULTURA E MEIO AMBIENTE</t>
         </is>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" s="4">
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - DEP. ACADEM. DE AGRICULTURA E MEIO AMBIENTE</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>26100</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1" s="4">
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - PRODUÇÃO AGRÍCOLA</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>26101</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" s="4">
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - PRODUÇÃO AGRÍCOLA / HORTO FLORESTAL</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>26102</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="4">
       <c r="B78" s="3" t="inlineStr">
         <is>
+          <t>DAAA - DEP. ACADEM. DE AGRICULTURA E MEIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>26100</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" s="4">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - PRODUÇÃO AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>26101</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="4">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - PRODUÇÃO AGRÍCOLA / HORTO FLORESTAL</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>26102</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" s="4">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
           <t>LABORATORIOS</t>
         </is>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" s="4">
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - LABORATÓRIO DE MERISTEMA</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>26103</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" s="4">
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - LABORATÓRIO DE PROPAGAÇÃO DE PLANTAS</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>26104</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" s="4">
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - LABORATÓRIO DE ANÁLISE DE SOLOS</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>26105</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="4">
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>DAAA - LABORATÓRIO DE PRÁTICA DE SOLOS</t>
+          <t>DAAA - LABORATÓRIO DE MERISTEMA</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>26113</v>
+        <v>26103</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="4">
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>DAAA - LABORATORIO DE CALDAS</t>
+          <t>DAAA - LABORATÓRIO DE PROPAGAÇÃO DE PLANTAS</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>26119</v>
+        <v>26104</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="4">
       <c r="C84" s="3" t="inlineStr">
         <is>
+          <t>DAAA - LABORATÓRIO DE ANÁLISE DE SOLOS</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>26105</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="4">
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - LABORATÓRIO DE PRÁTICA DE SOLOS</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>26113</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="4">
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - LABORATORIO DE CALDAS</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>26119</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" s="4">
+      <c r="C87" s="3" t="inlineStr">
+        <is>
           <t>DAAA - LABORATORIO DE ECOLOGIA</t>
         </is>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E87" s="3" t="n">
         <v>26123</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" s="4">
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - AGRICULTURA - SALA 02</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>26106</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" s="4">
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - AGRICULTURA - SALA 03</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>26107</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" s="4">
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - AGRONOMIA - LABORATÓRIO DE MICROBIOLOGIA</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>26108</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="4">
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>DAAA - RECEPÇÃO PRÉDIO 1 - AGRONOMIA</t>
+          <t>DAAA - AGRICULTURA - SALA 02</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>26109</v>
+        <v>26106</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="4">
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>DAAA - AGRICULTURA - SALA PROFESSORES (AO LADO DA SALA 4)</t>
+          <t>DAAA - AGRICULTURA - SALA 03</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>26110</v>
+        <v>26107</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="4">
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>DAAA - NEA - NUCLEO DE ESTUDOS DA AGROECOLOGIA (GAIOLA)</t>
+          <t>DAAA - AGRONOMIA - LABORATÓRIO DE MICROBIOLOGIA</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>26111</v>
+        <v>26108</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="4">
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>DAAA - AGRICULTURA - SALA 04</t>
+          <t>DAAA - RECEPÇÃO PRÉDIO 1 - AGRONOMIA</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>26112</v>
+        <v>26109</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="4">
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>DAAA - AGRICULTURA - COZINHA</t>
+          <t>DAAA - AGRICULTURA - SALA PROFESSORES (AO LADO DA SALA 4)</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>26114</v>
+        <v>26110</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1" s="4">
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>DAAA - AGRICULTURA</t>
-        </is>
+          <t>DAAA - NEA - NUCLEO DE ESTUDOS DA AGROECOLOGIA (GAIOLA)</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>26111</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="4">
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - AGRICULTURA - SALA 01</t>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - AGRICULTURA - SALA 04</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>26115</v>
+        <v>26112</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="4">
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - AGRICULTURA - SALA 04</t>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - AGRICULTURA - COZINHA</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>26116</v>
+        <v>26114</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="4">
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>DAAA - SALA DA GERENCIA DO DAAA</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>26117</v>
+          <t>DAAA - AGRICULTURA</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="4">
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - DEPOSITO DE FERRAMENTAS E TOPOGRAFIA</t>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - AGRICULTURA - SALA 01</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>26118</v>
+        <v>26115</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="4">
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - OLERICULTURA 1</t>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - AGRICULTURA - SALA 04</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>26120</v>
+        <v>26116</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="4">
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>DAAA - OLERICULTURA 2</t>
+          <t>DAAA - SALA DA GERENCIA DO DAAA</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>26121</v>
+        <v>26117</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="4">
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>DAAA - GALPAO DE ARMAZENAMENTO DE FRUTAS E SEMENTES</t>
+          <t>DAAA - DEPOSITO DE FERRAMENTAS E TOPOGRAFIA</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>26122</v>
+        <v>26118</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="4">
       <c r="B101" s="3" t="inlineStr">
         <is>
+          <t>DAAA - OLERICULTURA 1</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>26120</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1" s="4">
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - OLERICULTURA 2</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>26121</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1" s="4">
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - GALPAO DE ARMAZENAMENTO DE FRUTAS E SEMENTES</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>26122</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1" s="4">
+      <c r="B104" s="3" t="inlineStr">
+        <is>
           <t>DAAA - PREDIO 1</t>
         </is>
-      </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1" s="4">
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - PREDIO 1 - VARANDA</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>26124</v>
-      </c>
-    </row>
-    <row r="103" ht="15.75" customHeight="1" s="4">
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - PREDIO 1 - SALA DOS PROFESSORES</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>26125</v>
-      </c>
-    </row>
-    <row r="104" ht="15.75" customHeight="1" s="4">
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - PREDIO 1 - LABORATORIO MULTIUSO</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>26126</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1" s="4">
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>DAAA - PREDIO 1 - SALA 1</t>
+          <t>DAAA - PREDIO 1 - VARANDA</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>26127</v>
+        <v>26124</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="4">
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>DAAA - PREDIO 1 - SALA 2</t>
+          <t>DAAA - PREDIO 1 - SALA DOS PROFESSORES</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>26128</v>
+        <v>26125</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1" s="4">
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>DAAA - PREDIO 1 - SALA 3</t>
+          <t>DAAA - PREDIO 1 - LABORATORIO MULTIUSO</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>26129</v>
+        <v>26126</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1" s="4">
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - PREDIO 2</t>
-        </is>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - PREDIO 1 - SALA 1</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>26127</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1" s="4">
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>DAAA - PREDIO 2 - LABORATORIO DE PLANTAS</t>
+          <t>DAAA - PREDIO 1 - SALA 2</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>26130</v>
+        <v>26128</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1" s="4">
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>DAAA - PREDIO 2 - SALA DE AULA</t>
+          <t>DAAA - PREDIO 1 - SALA 3</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>26131</v>
+        <v>26129</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" s="4">
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>DAAA - PREDIO 2 - SALA DE HOMEOPATIA</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>26132</v>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - PREDIO 2</t>
+        </is>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="4">
       <c r="C112" s="3" t="inlineStr">
         <is>
+          <t>DAAA - PREDIO 2 - LABORATORIO DE PLANTAS</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>26130</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1" s="4">
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - PREDIO 2 - SALA DE AULA</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>26131</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1" s="4">
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>DAAA - PREDIO 2 - SALA DE HOMEOPATIA</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>26132</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1" s="4">
+      <c r="C115" s="3" t="inlineStr">
+        <is>
           <t>DAAA - PREDIO 2 - VARANDA</t>
         </is>
       </c>
-      <c r="E112" s="3" t="n">
+      <c r="E115" s="3" t="n">
         <v>26133</v>
       </c>
     </row>
-    <row r="113" ht="15.75" customHeight="1" s="4">
-      <c r="A113" s="3" t="inlineStr">
+    <row r="116" ht="15.75" customHeight="1" s="4">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>DACC - DEP. ACADEMICO DE CIENCIA DA COMPUTACAO</t>
         </is>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1" s="4">
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>DACC - DEP. ACADEMICO DE CIENCIA DA COMPUTACAO</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>26200</v>
-      </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1" s="4">
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>DACC -  LAB.INF.01 - PREDIO CENTRAL</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>26201</v>
-      </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1" s="4">
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>DACC - LAB.INF.02 - PREDIO CENTRAL</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>26202</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1" s="4">
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>DACC - LAB.INF.03 - PREDIO CENTRAL</t>
+          <t>DACC - DEP. ACADEMICO DE CIENCIA DA COMPUTACAO</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>26203</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1" s="4">
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>DACC - LAB.INF.04 - PREDIO CENTRAL</t>
+          <t>DACC -  LAB.INF.01 - PREDIO CENTRAL</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>26204</v>
+        <v>26201</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="4">
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>DACC - LAB.INF.05 - PREDIO CENTRAL</t>
+          <t>DACC - LAB.INF.02 - PREDIO CENTRAL</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>26205</v>
+        <v>26202</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1" s="4">
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>DACC - LAB.INF.06</t>
+          <t>DACC - LAB.INF.03 - PREDIO CENTRAL</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>26206</v>
+        <v>26203</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1" s="4">
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>DACC - LAB.INF.07</t>
+          <t>DACC - LAB.INF.04 - PREDIO CENTRAL</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>26207</v>
+        <v>26204</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1" s="4">
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>DACC - HALL</t>
+          <t>DACC - LAB.INF.05 - PREDIO CENTRAL</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>26208</v>
+        <v>26205</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="4">
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>DACC - SALA DE ESTUDOS</t>
+          <t>DACC - LAB.INF.06</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>26209</v>
+        <v>26206</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1" s="4">
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>DACC - SALA DOS PROFESSORES</t>
+          <t>DACC - LAB.INF.07</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>26210</v>
+        <v>26207</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1" s="4">
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>DACC - SALA 01</t>
+          <t>DACC - HALL</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>26211</v>
+        <v>26208</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1" s="4">
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>DACC - SALA 02</t>
+          <t>DACC - SALA DE ESTUDOS</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>26212</v>
+        <v>26209</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1" s="4">
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>DACC - SALA DE SERVICOS</t>
+          <t>DACC - SALA DOS PROFESSORES</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>26213</v>
+        <v>26210</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1" s="4">
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>DACC - SALA DE ALMOXARIFADO</t>
+          <t>DACC - SALA 01</t>
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>26214</v>
+        <v>26211</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="4">
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>DACC - IF GNU - PREDIO CENTRAL</t>
+          <t>DACC - SALA 02</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>26215</v>
+        <v>26212</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="4">
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>DACC - ECOMP</t>
+          <t>DACC - SALA DE SERVICOS</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>26216</v>
+        <v>26213</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="4">
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>DACC - IPCA - LAB. GEOPROCESSANTO E EST. METEREOLOG.</t>
+          <t>DACC - SALA DE ALMOXARIFADO</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>26217</v>
+        <v>26214</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="4">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>DACG - DEP. ACADEMICO DE CIENCIAS GERENCIAIS</t>
-        </is>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>DACC - IF GNU - PREDIO CENTRAL</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>26215</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="4">
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>DACG - DEP. ACADEMICO DE CIENCIAS GERENCIAIS</t>
+          <t>DACC - ECOMP</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>26300</v>
+        <v>26216</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="4">
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>DACG - SALAS DE AULA</t>
+          <t>DACC - IPCA - LAB. GEOPROCESSANTO E EST. METEREOLOG.</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>26301</v>
+        <v>26217</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="4">
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>DACG - SALA DE REUNIOES</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>26302</v>
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>DACG - DEP. ACADEMICO DE CIENCIAS GERENCIAIS</t>
+        </is>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="4">
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>DACG - SALA DE PROFESSORES 01</t>
+          <t>DACG - DEP. ACADEMICO DE CIENCIAS GERENCIAIS</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>26303</v>
+        <v>26300</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="4">
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>DACG - SALA DE PROFESSORES 02</t>
+          <t>DACG - SALAS DE AULA</t>
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>26304</v>
+        <v>26301</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="4">
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>DACG - LABORATORIO DE INFORMATICA</t>
+          <t>DACG - SALA DE REUNIOES</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>26305</v>
+        <v>26302</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1" s="4">
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>DACG - ALMOXARIFADO</t>
+          <t>DACG - SALA DE PROFESSORES 01</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>26306</v>
+        <v>26303</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="4">
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>DACG - CORREDORES</t>
+          <t>DACG - SALA DE PROFESSORES 02</t>
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>26307</v>
+        <v>26304</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="4">
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>DACG - SALA DE COORDENACAO DO CURSO DE ADM</t>
+          <t>DACG - LABORATORIO DE INFORMATICA</t>
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>26308</v>
+        <v>26305</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1" s="4">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>DCTA - DEP. ACADEMICO DE TECNOLOGIA DE ALIMENTOS</t>
-        </is>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>DACG - ALMOXARIFADO</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>26306</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1" s="4">
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>DCTA - DEP. ACADEMICO DE TECNOLOGIA DE ALIMENTOS</t>
+          <t>DACG - CORREDORES</t>
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>26400</v>
+        <v>26307</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="4">
       <c r="B144" s="3" t="inlineStr">
         <is>
+          <t>DACG - SALA DE COORDENACAO DO CURSO DE ADM</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>26308</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1" s="4">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>DCTA - DEP. ACADEMICO DE TECNOLOGIA DE ALIMENTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1" s="4">
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>DCTA - DEP. ACADEMICO DE TECNOLOGIA DE ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>26400</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1" s="4">
+      <c r="B147" s="3" t="inlineStr">
+        <is>
           <t>DCTA 1</t>
         </is>
-      </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1" s="4">
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>DCTA 1 - HALL</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>26401</v>
-      </c>
-    </row>
-    <row r="146" ht="15.75" customHeight="1" s="4">
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>DCTA 1 - CORREDOR</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>26402</v>
-      </c>
-    </row>
-    <row r="147" ht="15.75" customHeight="1" s="4">
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>DCTA 1 - SALA DE APOIO TECNICO</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>26403</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="4">
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>DCTA 1 - SALA DE AULA</t>
+          <t>DCTA 1 - HALL</t>
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>26404</v>
+        <v>26401</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="4">
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>DCTA 1 - SALA DE PROFESSORES 1</t>
+          <t>DCTA 1 - CORREDOR</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>26405</v>
+        <v>26402</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="4">
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>DCTA 1 - SALA DE PROFESSORES 2</t>
+          <t>DCTA 1 - SALA DE APOIO TECNICO</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>26406</v>
+        <v>26403</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="4">
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>DCTA 1 - LABORATORIO DE ANALISE FISICO-QUIMICA DE ALIMENTOS</t>
+          <t>DCTA 1 - SALA DE AULA</t>
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>26407</v>
+        <v>26404</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="4">
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>DCTA 1 - LABORATORIO DE PANIFICACAO E NOVOS PRODUTOS</t>
+          <t>DCTA 1 - SALA DE PROFESSORES 1</t>
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>26408</v>
+        <v>26405</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1" s="4">
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>DCTA 1 - LABORATORIO DE MICROBIOLOGIA</t>
+          <t>DCTA 1 - SALA DE PROFESSORES 2</t>
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>26409</v>
+        <v>26406</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="4">
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>DCTA 1 - SOTAO</t>
+          <t>DCTA 1 - LABORATORIO DE ANALISE FISICO-QUIMICA DE ALIMENTOS</t>
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>26410</v>
+        <v>26407</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="4">
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>DCTA 1 - DEPOSITO DE MATERIAL DE LIMPEZA</t>
+          <t>DCTA 1 - LABORATORIO DE PANIFICACAO E NOVOS PRODUTOS</t>
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>26411</v>
+        <v>26408</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1" s="4">
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>DCTA 2</t>
-        </is>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>DCTA 1 - LABORATORIO DE MICROBIOLOGIA</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>26409</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1" s="4">
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>DCTA 2 - SALA DE AULA</t>
+          <t>DCTA 1 - SOTAO</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>26412</v>
+        <v>26410</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1" s="4">
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>DCTA 2 - SALA DE PROFESSORES 1</t>
+          <t>DCTA 1 - DEPOSITO DE MATERIAL DE LIMPEZA</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>26413</v>
+        <v>26411</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1" s="4">
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>DCTA 2 - SALA DE PROFESSORES 2</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>26414</v>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>DCTA 2</t>
+        </is>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1" s="4">
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>DCTA 3</t>
-        </is>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>DCTA 2 - SALA DE AULA</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>26412</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1" s="4">
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - HALL</t>
+          <t>DCTA 2 - SALA DE PROFESSORES 1</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>26415</v>
+        <v>26413</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1" s="4">
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - SALA DE AULA</t>
+          <t>DCTA 2 - SALA DE PROFESSORES 2</t>
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>26416</v>
+        <v>26414</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1" s="4">
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>DCTA 3 - SALA DE PROFESSORES 1</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>26417</v>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>DCTA 3</t>
+        </is>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1" s="4">
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - SALA DE PROFESSORES 2</t>
+          <t>DCTA 3 - HALL</t>
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>26418</v>
+        <v>26415</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1" s="4">
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - LABORATORIO DE MICROBIOLOGIA</t>
+          <t>DCTA 3 - SALA DE AULA</t>
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>26419</v>
+        <v>26416</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1" s="4">
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - LABORATORIO DE ANALISE FISICO-QUIMICA DE ALIMENTOS</t>
+          <t>DCTA 3 - SALA DE PROFESSORES 1</t>
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>26420</v>
+        <v>26417</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1" s="4">
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - LABORATORIO SENSORIAL</t>
+          <t>DCTA 3 - SALA DE PROFESSORES 2</t>
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>26421</v>
+        <v>26418</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1" s="4">
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - LABORATORIO DE BIOLOGIA MOLECULAR</t>
+          <t>DCTA 3 - LABORATORIO DE MICROBIOLOGIA</t>
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>26422</v>
+        <v>26419</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1" s="4">
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - ALMOXARIFADO 1 - REAGENTES QUÍMICOS</t>
+          <t>DCTA 3 - LABORATORIO DE ANALISE FISICO-QUIMICA DE ALIMENTOS</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>26423</v>
+        <v>26420</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1" s="4">
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - ALMOXARIFADO 2 - MEIOS DE CULTURA</t>
+          <t>DCTA 3 - LABORATORIO SENSORIAL</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>26424</v>
+        <v>26421</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1" s="4">
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - ALMOXARIFADO 3 - VIDRARIAS</t>
+          <t>DCTA 3 - LABORATORIO DE BIOLOGIA MOLECULAR</t>
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>26425</v>
+        <v>26422</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1" s="4">
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - ALMOXARIFADO 4 - PRODUTOS CONTROLADOS</t>
+          <t>DCTA 3 - ALMOXARIFADO 1 - REAGENTES QUÍMICOS</t>
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>26426</v>
+        <v>26423</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1" s="4">
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - ARMAZENAMENTO DE GAS</t>
+          <t>DCTA 3 - ALMOXARIFADO 2 - MEIOS DE CULTURA</t>
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>26427</v>
+        <v>26424</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1" s="4">
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>DCTA 3 - COZINHA</t>
+          <t>DCTA 3 - ALMOXARIFADO 3 - VIDRARIAS</t>
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>26428</v>
+        <v>26425</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1" s="4">
       <c r="C175" s="3" t="inlineStr">
         <is>
+          <t>DCTA 3 - ALMOXARIFADO 4 - PRODUTOS CONTROLADOS</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>26426</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1" s="4">
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>DCTA 3 - ARMAZENAMENTO DE GAS</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>26427</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1" s="4">
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>DCTA 3 - COZINHA</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>26428</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1" s="4">
+      <c r="C178" s="3" t="inlineStr">
+        <is>
           <t>DCTA 3 - ANEXO</t>
         </is>
       </c>
-      <c r="E175" s="3" t="n">
+      <c r="E178" s="3" t="n">
         <v>26429</v>
-      </c>
-    </row>
-    <row r="176" ht="15.75" customHeight="1" s="4">
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>DCTA - LABORATORIO DE EMBALAGENS</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>26430</v>
-      </c>
-    </row>
-    <row r="177" ht="15.75" customHeight="1" s="4">
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>DCTA - LABORATORIO DE PROCESSAMENTO DE ALIMENTOS</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>26431</v>
-      </c>
-    </row>
-    <row r="178" ht="15.75" customHeight="1" s="4">
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>DCTA - SETOR DE FRUTAS</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>26432</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1" s="4">
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>DCTA - SETOR DE CARNES</t>
+          <t>DCTA - LABORATORIO DE EMBALAGENS</t>
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>26433</v>
+        <v>26430</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1" s="4">
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>DCTA - CALDEIRA</t>
+          <t>DCTA - LABORATORIO DE PROCESSAMENTO DE ALIMENTOS</t>
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>26434</v>
+        <v>26431</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1" s="4">
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>DCTA - LABORATORIO DE QUIMICA E MEIO AMBIENTE</t>
+          <t>DCTA - SETOR DE FRUTAS</t>
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>26435</v>
+        <v>26432</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1" s="4">
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>DCTA - PROGRAMA DE PÓS GRADUAÇÃO EM CIÊNCIA E TECNOLOGIA DE ALIMENTOS</t>
+          <t>DCTA - SETOR DE CARNES</t>
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>26436</v>
+        <v>26433</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1" s="4">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>DAE - DEP. ACADEMICO DE EDUCACAO</t>
-        </is>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>DCTA - CALDEIRA</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>26434</v>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="4">
       <c r="B184" s="3" t="inlineStr">
         <is>
+          <t>DCTA - LABORATORIO DE QUIMICA E MEIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>26435</v>
+      </c>
+    </row>
+    <row r="185" ht="15.75" customHeight="1" s="4">
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>DCTA - PROGRAMA DE PÓS GRADUAÇÃO EM CIÊNCIA E TECNOLOGIA DE ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>26436</v>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1" s="4">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
           <t>DAE - DEP. ACADEMICO DE EDUCACAO</t>
         </is>
       </c>
-      <c r="E184" s="3" t="n">
+    </row>
+    <row r="187" ht="15.75" customHeight="1" s="4">
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>DAE - DEP. ACADEMICO DE EDUCACAO</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
         <v>26500</v>
       </c>
     </row>
-    <row r="185" ht="15.75" customHeight="1" s="4">
-      <c r="C185" s="3" t="inlineStr">
+    <row r="188" ht="15.75" customHeight="1" s="4">
+      <c r="C188" s="3" t="inlineStr">
         <is>
           <t>DAE - LABORATORIO DE BIOLOGIA (ANTIGO ALOJAMENTO / BLOCO B / SALA 2)</t>
         </is>
       </c>
-      <c r="E185" s="3" t="n">
+      <c r="E188" s="3" t="n">
         <v>26501</v>
       </c>
     </row>
-    <row r="186" ht="15.75" customHeight="1" s="4">
-      <c r="C186" s="3" t="inlineStr">
+    <row r="189" ht="15.75" customHeight="1" s="4">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>DAE - SALA DE ARTES (ALOJAM./BLOCOB/SALA 8)</t>
         </is>
       </c>
-      <c r="E186" s="3" t="n">
+      <c r="E189" s="3" t="n">
         <v>26502</v>
       </c>
     </row>
-    <row r="187" ht="15.75" customHeight="1" s="4">
-      <c r="A187" s="3" t="inlineStr">
+    <row r="190" ht="15.75" customHeight="1" s="4">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>DEMAFE - DEP. ACADEMICO DE MATEMATICA E FISICA</t>
         </is>
-      </c>
-    </row>
-    <row r="188" ht="15.75" customHeight="1" s="4">
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>DEMAFE - DEP. ACADEMICO DE MATEMATICA E FISICA</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="n">
-        <v>26600</v>
-      </c>
-    </row>
-    <row r="189" ht="15.75" customHeight="1" s="4">
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>DEMAFE - LABORATORIO DE FISICA</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>26601</v>
-      </c>
-    </row>
-    <row r="190" ht="15.75" customHeight="1" s="4">
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>DEMAFE - LABORATORIO DE INFORMÁTICA</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>26602</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1" s="4">
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - LABORATÓRIO DE MATEMÁTICA</t>
+          <t>DEMAFE - DEP. ACADEMICO DE MATEMATICA E FISICA</t>
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>26603</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1" s="4">
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2</t>
+          <t>DEMAFE - LABORATORIO DE FISICA</t>
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>26604</v>
+        <v>26601</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" s="4">
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 1</t>
+          <t>DEMAFE - LABORATORIO DE INFORMÁTICA</t>
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>26605</v>
+        <v>26602</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1" s="4">
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 2</t>
+          <t>DEMAFE - LABORATÓRIO DE MATEMÁTICA</t>
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>26606</v>
+        <v>26603</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" s="4">
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 3</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 2</t>
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>26607</v>
+        <v>26604</v>
       </c>
     </row>
     <row r="196" ht="15.75" customHeight="1" s="4">
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 4</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 1</t>
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>26608</v>
+        <v>26605</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1" s="4">
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE REUNIÃO</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 2</t>
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>26609</v>
+        <v>26606</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1" s="4">
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 3</t>
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>26610</v>
+        <v>26607</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1" s="4">
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 1</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 4</t>
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>26611</v>
+        <v>26608</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1" s="4">
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 2</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE REUNIÃO</t>
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>26612</v>
+        <v>26609</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1" s="4">
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 3</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 3</t>
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>26613</v>
+        <v>26610</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1" s="4">
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 4</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 1</t>
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>26614</v>
+        <v>26611</v>
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1" s="4">
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 5</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 2</t>
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>26615</v>
+        <v>26612</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1" s="4">
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 6</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 3</t>
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>26616</v>
+        <v>26613</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1" s="4">
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>SALA DE AULA 4</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 4</t>
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>26617</v>
+        <v>26614</v>
       </c>
     </row>
     <row r="206" ht="15.75" customHeight="1" s="4">
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>SALA DE AULA 5</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 5</t>
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>26618</v>
+        <v>26615</v>
       </c>
     </row>
     <row r="207" ht="15.75" customHeight="1" s="4">
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>SALA DE AULA 6</t>
+          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 6</t>
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>26619</v>
+        <v>26616</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1" s="4">
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>DMAFE - IPCA - LAB PESQUISA ENS DE MAT - LAPEM</t>
+          <t>SALA DE AULA 4</t>
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>26620</v>
+        <v>26617</v>
       </c>
     </row>
     <row r="209" ht="15.75" customHeight="1" s="4">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>DZO - DEP. ACADEMICO DE ZOOTECNIA</t>
-        </is>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>SALA DE AULA 5</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>26618</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1" s="4">
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>DZO - DEP. ACADEMICO DE ZOOTECNIA</t>
+          <t>SALA DE AULA 6</t>
         </is>
       </c>
       <c r="E210" s="3" t="n">
-        <v>26700</v>
+        <v>26619</v>
       </c>
     </row>
     <row r="211" ht="15.75" customHeight="1" s="4">
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>DZO - PREDIO DA ZOOTECNIA - SALA 1</t>
+          <t>DMAFE - IPCA - LAB PESQUISA ENS DE MAT - LAPEM</t>
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>26701</v>
+        <v>26620</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1" s="4">
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>DZO - PREDIO DA ZOOTECNIA - SALA 2</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="n">
-        <v>26702</v>
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>DZO - DEP. ACADEMICO DE ZOOTECNIA</t>
+        </is>
       </c>
     </row>
     <row r="213" ht="15.75" customHeight="1" s="4">
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>DZO - PREDIO DA ZOOTECNIA - SALA 3</t>
+          <t>DZO - DEP. ACADEMICO DE ZOOTECNIA</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>26703</v>
+        <v>26700</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1" s="4">
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>DZO - ANFITEATRO 1 - SALA 4</t>
+          <t>DZO - PREDIO DA ZOOTECNIA - SALA 1</t>
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>26704</v>
+        <v>26701</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1" s="4">
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>DZO - ANFITEATRO 2 - SALA 5</t>
+          <t>DZO - PREDIO DA ZOOTECNIA - SALA 2</t>
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>26705</v>
+        <v>26702</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1" s="4">
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA DE PROFESSORES E REUNIÃO</t>
+          <t>DZO - PREDIO DA ZOOTECNIA - SALA 3</t>
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>26707</v>
+        <v>26703</v>
       </c>
     </row>
     <row r="217" ht="15.75" customHeight="1" s="4">
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 6</t>
+          <t>DZO - ANFITEATRO 1 - SALA 4</t>
         </is>
       </c>
       <c r="E217" s="3" t="n">
-        <v>26708</v>
+        <v>26704</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1" s="4">
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 7</t>
+          <t>DZO - ANFITEATRO 2 - SALA 5</t>
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>26709</v>
+        <v>26705</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1" s="4">
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>DZO - PREDIO DA ZOOTECNIA - SALA DOS PROFESSORES 1</t>
+          <t>DZO - SALA DE PROFESSORES E REUNIÃO</t>
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>26710</v>
+        <v>26707</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1" s="4">
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>DZO - PREDIO DA ZOOTECNIA - SALA DOS PROFESSORES 2</t>
+          <t>DZO - SALA 6</t>
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>26711</v>
+        <v>26708</v>
       </c>
     </row>
     <row r="221" ht="15.75" customHeight="1" s="4">
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA DE PROFESSORES E REUNIAO</t>
+          <t>DZO - SALA 7</t>
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>26712</v>
+        <v>26709</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1" s="4">
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALAS PROF / COZ / LAB PEIXES - CASA ANTIGA</t>
+          <t>DZO - PREDIO DA ZOOTECNIA - SALA DOS PROFESSORES 1</t>
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>26713</v>
+        <v>26710</v>
       </c>
     </row>
     <row r="223" ht="15.75" customHeight="1" s="4">
       <c r="B223" s="3" t="inlineStr">
         <is>
+          <t>DZO - PREDIO DA ZOOTECNIA - SALA DOS PROFESSORES 2</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>26711</v>
+      </c>
+    </row>
+    <row r="224" ht="15.75" customHeight="1" s="4">
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>DZO - SALA DE PROFESSORES E REUNIAO</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>26712</v>
+      </c>
+    </row>
+    <row r="225" ht="15.75" customHeight="1" s="4">
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>DZO - SALAS PROF / COZ / LAB PEIXES - CASA ANTIGA</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>26713</v>
+      </c>
+    </row>
+    <row r="226" ht="15.75" customHeight="1" s="4">
+      <c r="B226" s="3" t="inlineStr">
+        <is>
           <t>DZO - PREDIO DA ZOOTECNIA</t>
         </is>
-      </c>
-    </row>
-    <row r="224" ht="15.75" customHeight="1" s="4">
-      <c r="C224" s="3" t="inlineStr">
-        <is>
-          <t>DZO - PREDIO ZOOTECNIA - LAB. HISTOLOGIA E PARASIT</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="n">
-        <v>26714</v>
-      </c>
-    </row>
-    <row r="225" ht="15.75" customHeight="1" s="4">
-      <c r="C225" s="3" t="inlineStr">
-        <is>
-          <t>DZO - PREDIO DA ZOOTECNIA- LAB. DE INFORMATICA</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="n">
-        <v>26715</v>
-      </c>
-    </row>
-    <row r="226" ht="15.75" customHeight="1" s="4">
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>DZO - PREDIO DA ZOOTECNIA - SALA 9</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="n">
-        <v>26717</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1" s="4">
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 1 - LABORATORIO DE BROMATOLOGIA</t>
+          <t>DZO - PREDIO ZOOTECNIA - LAB. HISTOLOGIA E PARASIT</t>
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>26718</v>
+        <v>26714</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1" s="4">
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 2 - LABORATORIO ANATOMIA ANIMAL</t>
+          <t>DZO - PREDIO DA ZOOTECNIA- LAB. DE INFORMATICA</t>
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>26719</v>
+        <v>26715</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1" s="4">
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>DZO - SALA 3 - LABORATORIO ANALISES ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="n">
-        <v>26720</v>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>DZO - PREDIO DA ZOOTECNIA - VARANDA E CORREDORES</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>26716</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1" s="4">
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 4 - ESCRITORIO</t>
+          <t>DZO - PREDIO DA ZOOTECNIA - SALA 9</t>
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>26721</v>
+        <v>26717</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1" s="4">
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 5 / 9- MOINHOS, ESTUFAS E FREEZERS</t>
+          <t>DZO - SALA 1 - LABORATORIO DE BROMATOLOGIA</t>
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>26722</v>
+        <v>26718</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1" s="4">
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 6 / 7 - ALMOXARIFADO</t>
+          <t>DZO - SALA 2 - LABORATORIO ANATOMIA ANIMAL</t>
         </is>
       </c>
       <c r="E232" s="3" t="n">
-        <v>26723</v>
+        <v>26719</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1" s="4">
       <c r="C233" s="3" t="inlineStr">
         <is>
+          <t>DZO - SALA 3 - LABORATORIO ANALISES ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>26720</v>
+      </c>
+    </row>
+    <row r="234" ht="15.75" customHeight="1" s="4">
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>DZO - SALA 4 - ESCRITORIO</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>26721</v>
+      </c>
+    </row>
+    <row r="235" ht="15.75" customHeight="1" s="4">
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>DZO - SALA 5 / 9- MOINHOS, ESTUFAS E FREEZERS</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>26722</v>
+      </c>
+    </row>
+    <row r="236" ht="15.75" customHeight="1" s="4">
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>DZO - SALA 6 / 7 - ALMOXARIFADO</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>26723</v>
+      </c>
+    </row>
+    <row r="237" ht="15.75" customHeight="1" s="4">
+      <c r="C237" s="3" t="inlineStr">
+        <is>
           <t>DZO - SALA 6</t>
         </is>
       </c>
-      <c r="E233" s="3" t="n">
+      <c r="E237" s="3" t="n">
         <v>26706</v>
-      </c>
-    </row>
-    <row r="234" ht="15.75" customHeight="1" s="4">
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>DZO - SALA 8 - COZINHA/ CORREDOR</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="n">
-        <v>26724</v>
-      </c>
-    </row>
-    <row r="235" ht="15.75" customHeight="1" s="4">
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>DZO - SALA 10 - DEPOSITO</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="n">
-        <v>26725</v>
-      </c>
-    </row>
-    <row r="236" ht="15.75" customHeight="1" s="4">
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>DZO - GERENCIA DE PRODUCAO ZOOTECNIA</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="n">
-        <v>26726</v>
-      </c>
-    </row>
-    <row r="237" ht="15.75" customHeight="1" s="4">
-      <c r="B237" s="3" t="inlineStr">
-        <is>
-          <t>DZO - FRANGO- POSTURA / COTURNICULTURA</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="n">
-        <v>26727</v>
       </c>
     </row>
     <row r="238" ht="15.75" customHeight="1" s="4">
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>DZO - PSICULTURA</t>
+          <t>DZO - SALA 8 - COZINHA/ CORREDOR</t>
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>26728</v>
+        <v>26724</v>
       </c>
     </row>
     <row r="239" ht="15.75" customHeight="1" s="4">
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>DZO - ABATEDOURO / ORDENHA /ESTABULO</t>
+          <t>DZO - SALA 10 - DEPOSITO</t>
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>26729</v>
+        <v>26725</v>
       </c>
     </row>
     <row r="240" ht="15.75" customHeight="1" s="4">
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>DZO - FABRICA DE RACAO</t>
+          <t>DZO - GERENCIA DE PRODUCAO ZOOTECNIA</t>
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>26730</v>
+        <v>26726</v>
       </c>
     </row>
     <row r="241" ht="15.75" customHeight="1" s="4">
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>DZO - DEPOSITO DA ZOOTECNIA - PAIOL</t>
+          <t>DZO - FRANGO- POSTURA / COTURNICULTURA</t>
         </is>
       </c>
       <c r="E241" s="3" t="n">
-        <v>26731</v>
+        <v>26727</v>
       </c>
     </row>
     <row r="242" ht="15.75" customHeight="1" s="4">
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>DZO - DEPOSITO EQUINOCULTURA</t>
+          <t>DZO - PSICULTURA</t>
         </is>
       </c>
       <c r="E242" s="3" t="n">
-        <v>26732</v>
+        <v>26728</v>
       </c>
     </row>
     <row r="243" ht="15.75" customHeight="1" s="4">
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA VETERINARIO</t>
+          <t>DZO - ABATEDOURO / ORDENHA /ESTABULO</t>
         </is>
       </c>
       <c r="E243" s="3" t="n">
-        <v>26733</v>
+        <v>26729</v>
       </c>
     </row>
     <row r="244" ht="15.75" customHeight="1" s="4">
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>DZO - SUINOCULTURA / INSEMINACAO ART / SL ADM</t>
+          <t>DZO - FABRICA DE RACAO</t>
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>26734</v>
+        <v>26730</v>
       </c>
     </row>
     <row r="245" ht="15.75" customHeight="1" s="4">
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>DZO - PIGMAKER</t>
+          <t>DZO - DEPOSITO DA ZOOTECNIA - PAIOL</t>
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>26735</v>
+        <v>26731</v>
       </c>
     </row>
     <row r="246" ht="15.75" customHeight="1" s="4">
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA MESTRADO</t>
+          <t>DZO - DEPOSITO EQUINOCULTURA</t>
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>26736</v>
+        <v>26732</v>
       </c>
     </row>
     <row r="247" ht="15.75" customHeight="1" s="4">
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>DZO - GALPAO EXPERIMENTAL DE AVICULTURA</t>
+          <t>DZO - SALA VETERINARIO</t>
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>26737</v>
+        <v>26733</v>
       </c>
     </row>
     <row r="248" ht="15.75" customHeight="1" s="4">
-      <c r="A248" s="3" t="inlineStr">
-        <is>
-          <t>NUCLEO DE EDUCACAO FISICA E SAUDE</t>
-        </is>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>DZO - SUINOCULTURA / INSEMINACAO ART / SL ADM</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>26734</v>
       </c>
     </row>
     <row r="249" ht="15.75" customHeight="1" s="4">
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>NEFI - NUCLEO DE EDUCACAO FISICA</t>
+          <t>DZO - PIGMAKER</t>
         </is>
       </c>
       <c r="E249" s="3" t="n">
-        <v>26800</v>
+        <v>26735</v>
       </c>
     </row>
     <row r="250" ht="15.75" customHeight="1" s="4">
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>ACADEMIA</t>
+          <t>DZO - SALA MESTRADO</t>
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>26801</v>
+        <v>26736</v>
       </c>
     </row>
     <row r="251" ht="15.75" customHeight="1" s="4">
       <c r="B251" s="3" t="inlineStr">
         <is>
+          <t>DZO - GALPAO EXPERIMENTAL DE AVICULTURA</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>26737</v>
+      </c>
+    </row>
+    <row r="252" ht="15.75" customHeight="1" s="4">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>DZO - GALPAO EXPERIMENTAL DE BOVINOCULTURA</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>26738</v>
+      </c>
+    </row>
+    <row r="253" ht="15.75" customHeight="1" s="4">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>DZO - CUNICULTURA - COELHOS</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>26739</v>
+      </c>
+    </row>
+    <row r="254" ht="15.75" customHeight="1" s="4">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DZO - LABORATORIO OVINOCAPRINOCULTURA</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>26740</v>
+      </c>
+    </row>
+    <row r="255" ht="15.75" customHeight="1" s="4">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>DZO - FRANGO - CORTE</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>26741</v>
+      </c>
+    </row>
+    <row r="256" ht="15.75" customHeight="1" s="4">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>DZO - CAPRINOCULTURA</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>26742</v>
+      </c>
+    </row>
+    <row r="257" ht="15.75" customHeight="1" s="4">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>DZO - DEPOSITOS E SALA DE APOIO LAB OVINOCAPRINO</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>26743</v>
+      </c>
+    </row>
+    <row r="258" ht="15.75" customHeight="1" s="4">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>DZO - APICULTURA</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>26744</v>
+      </c>
+    </row>
+    <row r="259" ht="15.75" customHeight="1" s="4">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>DZO - SEMOVENTES</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>26745</v>
+      </c>
+    </row>
+    <row r="260" ht="15.75" customHeight="1" s="4">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>NUCLEO DE EDUCACAO FISICA E SAUDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="15.75" customHeight="1" s="4">
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>NEFI - NUCLEO DE EDUCACAO FISICA</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>26800</v>
+      </c>
+    </row>
+    <row r="262" ht="15.75" customHeight="1" s="4">
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>ACADEMIA</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>26801</v>
+      </c>
+    </row>
+    <row r="263" ht="15.75" customHeight="1" s="4">
+      <c r="B263" s="3" t="inlineStr">
+        <is>
           <t>QUADRA POLIESPORTIVA 1</t>
         </is>
       </c>
-      <c r="E251" s="3" t="n">
+      <c r="E263" s="3" t="n">
         <v>26803</v>
       </c>
     </row>
-    <row r="252" ht="15.75" customHeight="1" s="4">
-      <c r="B252" s="3" t="inlineStr">
+    <row r="264" ht="15.75" customHeight="1" s="4">
+      <c r="B264" s="3" t="inlineStr">
         <is>
           <t>QUADRA POLIESPORTIVA 2</t>
         </is>
       </c>
-      <c r="E252" s="3" t="n">
+      <c r="E264" s="3" t="n">
         <v>26804</v>
-      </c>
-    </row>
-    <row r="253" ht="15.75" customHeight="1" s="4">
-      <c r="B253" s="3" t="inlineStr">
-        <is>
-          <t>CENTRO DE TREINAMENTO DE TENIS DE MESA E LUTAS</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="n">
-        <v>26805</v>
-      </c>
-    </row>
-    <row r="254" ht="15.75" customHeight="1" s="4">
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>LABORATORIOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="15.75" customHeight="1" s="4">
-      <c r="C255" s="3" t="inlineStr">
-        <is>
-          <t>LABORATORIO DE MEDIDAS E AVALIACAO</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="n">
-        <v>26807</v>
-      </c>
-    </row>
-    <row r="256" ht="15.75" customHeight="1" s="4">
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>LABORATORIO DE CINEANTROPOMETRIA</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="n">
-        <v>26808</v>
-      </c>
-    </row>
-    <row r="257" ht="15.75" customHeight="1" s="4">
-      <c r="C257" s="3" t="inlineStr">
-        <is>
-          <t>LABORATORIO DE NUTRICAO APLICADA</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="n">
-        <v>26809</v>
-      </c>
-    </row>
-    <row r="258" ht="15.75" customHeight="1" s="4">
-      <c r="C258" s="3" t="inlineStr">
-        <is>
-          <t>LABORATORIO DE PRATICAS PEDAGOGICAS</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="n">
-        <v>26810</v>
-      </c>
-    </row>
-    <row r="259" ht="15.75" customHeight="1" s="4">
-      <c r="C259" s="3" t="inlineStr">
-        <is>
-          <t>EFI - ANATOMIA</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="n">
-        <v>26806</v>
-      </c>
-    </row>
-    <row r="260" ht="15.75" customHeight="1" s="4">
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>COORDENACAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="15.75" customHeight="1" s="4">
-      <c r="C261" s="3" t="inlineStr">
-        <is>
-          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA - SALA 1</t>
-        </is>
-      </c>
-      <c r="E261" s="3" t="n">
-        <v>26811</v>
-      </c>
-    </row>
-    <row r="262" ht="15.75" customHeight="1" s="4">
-      <c r="C262" s="3" t="inlineStr">
-        <is>
-          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA - SALA 2</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="n">
-        <v>26812</v>
-      </c>
-    </row>
-    <row r="263" ht="15.75" customHeight="1" s="4">
-      <c r="C263" s="3" t="inlineStr">
-        <is>
-          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA - SALA 3</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="n">
-        <v>26813</v>
-      </c>
-    </row>
-    <row r="264" ht="15.75" customHeight="1" s="4">
-      <c r="C264" s="3" t="inlineStr">
-        <is>
-          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA - SALA 4</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="n">
-        <v>26814</v>
       </c>
     </row>
     <row r="265" ht="15.75" customHeight="1" s="4">
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA</t>
+          <t>CENTRO DE TREINAMENTO DE TENIS DE MESA E LUTAS</t>
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>26802</v>
+        <v>26805</v>
       </c>
     </row>
     <row r="266" ht="15.75" customHeight="1" s="4">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>NUCLEO DE DIREITO</t>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>LABORATORIOS</t>
         </is>
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1" s="4">
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>NUCLEO DE DIREITO</t>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>LABORATORIO DE MEDIDAS E AVALIACAO</t>
         </is>
       </c>
       <c r="E267" s="3" t="n">
-        <v>26900</v>
+        <v>26807</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" s="4">
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>NUCLEO DE DIREITO - SALA DE AULA 1 - PRATICA JURIDICA</t>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>LABORATORIO DE CINEANTROPOMETRIA</t>
         </is>
       </c>
       <c r="E268" s="3" t="n">
-        <v>26901</v>
+        <v>26808</v>
       </c>
     </row>
     <row r="269" ht="15.75" customHeight="1" s="4">
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>PAPRE - POSTO DE ATENDIMENTO PRÉ PROCESSUAL</t>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>LABORATORIO DE NUTRICAO APLICADA</t>
         </is>
       </c>
       <c r="E269" s="3" t="n">
-        <v>26902</v>
+        <v>26809</v>
       </c>
     </row>
     <row r="270" ht="15.75" customHeight="1" s="4">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>DIRETORIA DE ADMINISTRACAO E PLANEJAMENTO</t>
-        </is>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>LABORATORIO DE PRATICAS PEDAGOGICAS</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>26810</v>
       </c>
     </row>
     <row r="271" ht="15.75" customHeight="1" s="4">
-      <c r="B271" s="3" t="inlineStr">
-        <is>
-          <t>DIRETORIA DE ADMINISTRACAO E PLANEJAMENTO</t>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>EFI - ANATOMIA</t>
         </is>
       </c>
       <c r="E271" s="3" t="n">
-        <v>30000</v>
+        <v>26806</v>
       </c>
     </row>
     <row r="272" ht="15.75" customHeight="1" s="4">
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>PREDIO ADMINISTRATIVO</t>
+          <t>COORDENACAO</t>
         </is>
       </c>
     </row>
     <row r="273" ht="15.75" customHeight="1" s="4">
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>PRÉDIO ADMINISTRATIVO - SALA DE REUNIAO</t>
+          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA - SALA 1</t>
         </is>
       </c>
       <c r="E273" s="3" t="n">
-        <v>30001</v>
+        <v>26811</v>
       </c>
     </row>
     <row r="274" ht="15.75" customHeight="1" s="4">
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>PREDIO ADMINISTRATIVO - SALA DIRETORIA DE ADMINISTRACAO</t>
+          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA - SALA 2</t>
         </is>
       </c>
       <c r="E274" s="3" t="n">
-        <v>30002</v>
+        <v>26812</v>
       </c>
     </row>
     <row r="275" ht="15.75" customHeight="1" s="4">
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>PREDIO ADMINISTRATIVO - CASU</t>
+          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA - SALA 3</t>
         </is>
       </c>
       <c r="E275" s="3" t="n">
-        <v>30003</v>
+        <v>26813</v>
       </c>
     </row>
     <row r="276" ht="15.75" customHeight="1" s="4">
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>PRÉDIO ADMINISTRATIVO - COPA</t>
+          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA - SALA 4</t>
         </is>
       </c>
       <c r="E276" s="3" t="n">
-        <v>30004</v>
+        <v>26814</v>
       </c>
     </row>
     <row r="277" ht="15.75" customHeight="1" s="4">
-      <c r="C277" s="3" t="inlineStr">
-        <is>
-          <t>PRÉDIO ADMINISTRATIVO - COPA - DEPÓSITO (INSTRUMENTOS MUSICAIS)</t>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>SALA COORDENAÇÃO DE GRADUACAO EM EDUCACAO FISICA</t>
         </is>
       </c>
       <c r="E277" s="3" t="n">
-        <v>30005</v>
+        <v>26802</v>
       </c>
     </row>
     <row r="278" ht="15.75" customHeight="1" s="4">
-      <c r="C278" s="3" t="inlineStr">
-        <is>
-          <t>PRÉDIO ADMINISTRATIVO - COPA - SALA DML TERCEIRIZADOS</t>
-        </is>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>30006</v>
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>NUCLEO DE DIREITO</t>
+        </is>
       </c>
     </row>
     <row r="279" ht="15.75" customHeight="1" s="4">
-      <c r="C279" s="3" t="inlineStr">
-        <is>
-          <t>PRÉDIO ADMINISTRATIVO - SALA TELEFONISTA</t>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>NUCLEO DE DIREITO</t>
         </is>
       </c>
       <c r="E279" s="3" t="n">
-        <v>30007</v>
+        <v>26900</v>
       </c>
     </row>
     <row r="280" ht="15.75" customHeight="1" s="4">
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>GUARITA 1 - IGREJINHA</t>
+          <t>NUCLEO DE DIREITO - SALA DE AULA 1 - PRATICA JURIDICA</t>
         </is>
       </c>
       <c r="E280" s="3" t="n">
-        <v>30008</v>
+        <v>26901</v>
       </c>
     </row>
     <row r="281" ht="15.75" customHeight="1" s="4">
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>GUARITA 2 - AGRICULTURA</t>
+          <t>PAPRE - POSTO DE ATENDIMENTO PRÉ PROCESSUAL</t>
         </is>
       </c>
       <c r="E281" s="3" t="n">
-        <v>30009</v>
+        <v>26902</v>
       </c>
     </row>
     <row r="282" ht="15.75" customHeight="1" s="4">
-      <c r="B282" s="3" t="inlineStr">
-        <is>
-          <t>POSTO DE VIGILANCIA / VIGILANTE</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="n">
-        <v>30010</v>
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE ADMINISTRACAO E PLANEJAMENTO</t>
+        </is>
       </c>
     </row>
     <row r="283" ht="15.75" customHeight="1" s="4">
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>ALMOXARIFADO</t>
-        </is>
+          <t>DIRETORIA DE ADMINISTRACAO E PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="284" ht="15.75" customHeight="1" s="4">
-      <c r="C284" s="3" t="inlineStr">
-        <is>
-          <t>ALMOXARIFADO</t>
-        </is>
-      </c>
-      <c r="E284" s="3" t="n">
-        <v>31100</v>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>PREDIO ADMINISTRATIVO</t>
+        </is>
       </c>
     </row>
     <row r="285" ht="15.75" customHeight="1" s="4">
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>ALMOXARIFADO - SOTAO</t>
+          <t>PRÉDIO ADMINISTRATIVO - SALA DE REUNIAO</t>
         </is>
       </c>
       <c r="E285" s="3" t="n">
-        <v>31101</v>
+        <v>30001</v>
       </c>
     </row>
     <row r="286" ht="15.75" customHeight="1" s="4">
-      <c r="B286" s="3" t="inlineStr">
-        <is>
-          <t>PATRIMONIO</t>
-        </is>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>PREDIO ADMINISTRATIVO - SALA DIRETORIA DE ADMINISTRACAO</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="n">
+        <v>30002</v>
       </c>
     </row>
     <row r="287" ht="15.75" customHeight="1" s="4">
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>PATRIMONIO</t>
+          <t>PREDIO ADMINISTRATIVO - CASU</t>
         </is>
       </c>
       <c r="E287" s="3" t="n">
-        <v>31200</v>
+        <v>30003</v>
       </c>
     </row>
     <row r="288" ht="15.75" customHeight="1" s="4">
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>SALA PATRIMÔNIO</t>
+          <t>PRÉDIO ADMINISTRATIVO - COPA</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
-        <v>31201</v>
+        <v>30004</v>
       </c>
     </row>
     <row r="289" ht="15.75" customHeight="1" s="4">
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>PATRIMONIO - GALPAO 1</t>
+          <t>PRÉDIO ADMINISTRATIVO - COPA - DEPÓSITO (INSTRUMENTOS MUSICAIS)</t>
         </is>
       </c>
       <c r="E289" s="3" t="n">
-        <v>31202</v>
+        <v>30005</v>
       </c>
     </row>
     <row r="290" ht="15.75" customHeight="1" s="4">
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>PATRIMONIO - GALPAO 2 - AVALIACAO</t>
+          <t>PRÉDIO ADMINISTRATIVO - COPA - SALA DML TERCEIRIZADOS</t>
         </is>
       </c>
       <c r="E290" s="3" t="n">
-        <v>31203</v>
+        <v>30006</v>
       </c>
     </row>
     <row r="291" ht="15.75" customHeight="1" s="4">
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>PATRIMONIO - GALPAO 2 - DOACAO</t>
+          <t>PRÉDIO ADMINISTRATIVO - SALA TELEFONISTA</t>
         </is>
       </c>
       <c r="E291" s="3" t="n">
-        <v>31204</v>
+        <v>30007</v>
       </c>
     </row>
     <row r="292" ht="15.75" customHeight="1" s="4">
-      <c r="C292" s="3" t="inlineStr">
-        <is>
-          <t>PATRIMONIO - GALPAO 2 - IRRECUPERÁVEL</t>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>GUARITA 1 - IGREJINHA</t>
         </is>
       </c>
       <c r="E292" s="3" t="n">
-        <v>31205</v>
+        <v>30008</v>
       </c>
     </row>
     <row r="293" ht="15.75" customHeight="1" s="4">
-      <c r="C293" s="3" t="inlineStr">
-        <is>
-          <t>PATRIMONIO - LAVANDERIA - AVALIACAO</t>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>GUARITA 2 - AGRICULTURA</t>
         </is>
       </c>
       <c r="E293" s="3" t="n">
-        <v>31206</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="294" ht="15.75" customHeight="1" s="4">
-      <c r="C294" s="3" t="inlineStr">
-        <is>
-          <t>PATRIMONIO - LAVANDERIA - DOACAO</t>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>POSTO DE VIGILANCIA / VIGILANTE</t>
         </is>
       </c>
       <c r="E294" s="3" t="n">
-        <v>31207</v>
+        <v>30010</v>
       </c>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="4">
-      <c r="C295" s="3" t="inlineStr">
-        <is>
-          <t>PATRIMONIO - LAVANDERIA - IRRECUPERÁVEL</t>
-        </is>
-      </c>
-      <c r="E295" s="3" t="n">
-        <v>31208</v>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>COORDENACAO GERAL DE ADMINISTRACAO E FINANCAS</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>31000</v>
       </c>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="4">
-      <c r="C296" s="3" t="inlineStr">
-        <is>
-          <t>PATRIMONIO - ESCOLINHA</t>
-        </is>
-      </c>
-      <c r="E296" s="3" t="n">
-        <v>31209</v>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>ALMOXARIFADO</t>
+        </is>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="4">
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>REAVALIACAO - MATERIAL DE CONSUMO</t>
+          <t>ALMOXARIFADO</t>
         </is>
       </c>
       <c r="E297" s="3" t="n">
-        <v>31210</v>
+        <v>31100</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" s="4">
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>PATRIMONIO - GALPAO 2</t>
+          <t>ALMOXARIFADO - SOTAO</t>
         </is>
       </c>
       <c r="E298" s="3" t="n">
-        <v>31211</v>
+        <v>31101</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" s="4">
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>LICITACAO</t>
-        </is>
-      </c>
-      <c r="E299" s="3" t="n">
-        <v>31300</v>
+          <t>PATRIMONIO</t>
+        </is>
       </c>
     </row>
     <row r="300" ht="15.75" customHeight="1" s="4">
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>CONTRATOS</t>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>PATRIMONIO</t>
         </is>
       </c>
       <c r="E300" s="3" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="301" ht="15.75" customHeight="1" s="4">
-      <c r="B301" s="3" t="inlineStr">
-        <is>
-          <t>EXECUCAO FINANCEIRA</t>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>SALA PATRIMÔNIO</t>
         </is>
       </c>
       <c r="E301" s="3" t="n">
-        <v>31500</v>
+        <v>31201</v>
       </c>
     </row>
     <row r="302" ht="15.75" customHeight="1" s="4">
-      <c r="B302" s="3" t="inlineStr">
-        <is>
-          <t>CONTABILIDADE</t>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>PATRIMONIO - GALPAO 1</t>
         </is>
       </c>
       <c r="E302" s="3" t="n">
-        <v>31600</v>
+        <v>31202</v>
       </c>
     </row>
     <row r="303" ht="15.75" customHeight="1" s="4">
-      <c r="B303" s="3" t="inlineStr">
-        <is>
-          <t>TRANSPORTE</t>
-        </is>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>PATRIMONIO - GALPAO 2 - AVALIACAO</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>31203</v>
       </c>
     </row>
     <row r="304" ht="15.75" customHeight="1" s="4">
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>PATRIMONIO - GALPAO 2 - DOACAO</t>
         </is>
       </c>
       <c r="E304" s="3" t="n">
-        <v>31700</v>
+        <v>31204</v>
       </c>
     </row>
     <row r="305" ht="15.75" customHeight="1" s="4">
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>TRANSPORTE - SALA</t>
+          <t>PATRIMONIO - GALPAO 2 - IRRECUPERÁVEL</t>
         </is>
       </c>
       <c r="E305" s="3" t="n">
-        <v>31701</v>
+        <v>31205</v>
       </c>
     </row>
     <row r="306" ht="15.75" customHeight="1" s="4">
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>TRANSPORTE - GARAGEM</t>
+          <t>PATRIMONIO - LAVANDERIA - AVALIACAO</t>
         </is>
       </c>
       <c r="E306" s="3" t="n">
-        <v>31702</v>
+        <v>31206</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" s="4">
-      <c r="A307" s="3" t="inlineStr">
-        <is>
-          <t>DIRETORIA DE EXTENSÃO</t>
-        </is>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>PATRIMONIO - LAVANDERIA - DOACAO</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>31207</v>
       </c>
     </row>
     <row r="308" ht="15.75" customHeight="1" s="4">
-      <c r="B308" s="3" t="inlineStr">
-        <is>
-          <t>DIRETORIA DE EXTENSÃO</t>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>PATRIMONIO - LAVANDERIA - IRRECUPERÁVEL</t>
         </is>
       </c>
       <c r="E308" s="3" t="n">
-        <v>40000</v>
+        <v>31208</v>
       </c>
     </row>
     <row r="309" ht="15.75" customHeight="1" s="4">
-      <c r="B309" s="3" t="inlineStr">
-        <is>
-          <t>SARC - SEÇÃO DE ARTE E CULTURA</t>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>PATRIMONIO - ESCOLINHA</t>
         </is>
       </c>
       <c r="E309" s="3" t="n">
-        <v>41000</v>
+        <v>31209</v>
       </c>
     </row>
     <row r="310" ht="15.75" customHeight="1" s="4">
-      <c r="B310" s="3" t="inlineStr">
-        <is>
-          <t>SEÇÃO DE ESTÁGIO</t>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>REAVALIACAO - MATERIAL DE CONSUMO</t>
         </is>
       </c>
       <c r="E310" s="3" t="n">
-        <v>42000</v>
+        <v>31210</v>
       </c>
     </row>
     <row r="311" ht="15.75" customHeight="1" s="4">
-      <c r="B311" s="3" t="inlineStr">
-        <is>
-          <t>RELAÇÕES INSTITUCIONAIS</t>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>PATRIMONIO - GALPAO 2</t>
         </is>
       </c>
       <c r="E311" s="3" t="n">
-        <v>43000</v>
+        <v>31211</v>
       </c>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="4">
-      <c r="B312" s="3" t="inlineStr">
-        <is>
-          <t>SEÇÃO DE AÇÕES COMUNITÁRIAS</t>
-        </is>
-      </c>
-      <c r="E312" s="3" t="n">
-        <v>44000</v>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>PATRIMONIO - GALPAO 3 - IRRECUPERAVEL/ANTIECONOMIC</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>31212</v>
       </c>
     </row>
     <row r="313" ht="15.75" customHeight="1" s="4">
-      <c r="B313" s="3" t="inlineStr">
-        <is>
-          <t>SALA PROJETO PARTIU IF</t>
-        </is>
-      </c>
-      <c r="E313" s="3" t="n">
-        <v>44001</v>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>PATRIMONIO - GALPAO 3</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>31213</v>
       </c>
     </row>
     <row r="314" ht="15.75" customHeight="1" s="4">
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>SALA DA DIRETORIA DE EXTENSÃO</t>
+          <t>LICITACAO</t>
         </is>
       </c>
       <c r="E314" s="3" t="n">
-        <v>45000</v>
+        <v>31300</v>
       </c>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="4">
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>SALA DE REUNIÃO</t>
+          <t>CONTRATOS</t>
         </is>
       </c>
       <c r="E315" s="3" t="n">
-        <v>46000</v>
+        <v>31400</v>
       </c>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="4">
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>EMPRESA JUNIOR</t>
-        </is>
+          <t>EXECUCAO FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="n">
+        <v>31500</v>
       </c>
     </row>
     <row r="317" ht="15.75" customHeight="1" s="4">
-      <c r="C317" s="3" t="inlineStr">
-        <is>
-          <t>EMPRESA JUNIOR</t>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>CONTABILIDADE</t>
         </is>
       </c>
       <c r="E317" s="3" t="n">
-        <v>47000</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="318" ht="15.75" customHeight="1" s="4">
-      <c r="C318" s="3" t="inlineStr">
-        <is>
-          <t>EMPRESA JUNIOR AGROECO JR (ANTIGO ALOJAMENTO / BLOCO B / SALA 3)</t>
-        </is>
-      </c>
-      <c r="E318" s="3" t="n">
-        <v>47001</v>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>TRANSPORTE</t>
+        </is>
       </c>
     </row>
     <row r="319" ht="15.75" customHeight="1" s="4">
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>EMPRESA JUNIOR EMCOMP (ANTIGO ALOJAMENTO / BLOCO B / SALA 4)</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="E319" s="3" t="n">
-        <v>47002</v>
+        <v>31700</v>
       </c>
     </row>
     <row r="320" ht="15.75" customHeight="1" s="4">
-      <c r="B320" s="3" t="inlineStr">
-        <is>
-          <t>TEATRO (ANTIGO ALOJAMENTO/BLOCO B/SALA 5)</t>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>TRANSPORTE - SALA</t>
         </is>
       </c>
       <c r="E320" s="3" t="n">
-        <v>48000</v>
+        <v>31701</v>
       </c>
     </row>
     <row r="321" ht="15.75" customHeight="1" s="4">
-      <c r="A321" s="3" t="inlineStr">
-        <is>
-          <t>DIRETORIA DE PESQUISA E POS-GRADUACAO</t>
-        </is>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>TRANSPORTE - GARAGEM</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>31702</v>
       </c>
     </row>
     <row r="322" ht="15.75" customHeight="1" s="4">
-      <c r="B322" s="3" t="inlineStr">
-        <is>
-          <t>DIRETORIA DE PESQUISA E POS-GRADUACAO</t>
-        </is>
-      </c>
-      <c r="E322" s="3" t="n">
-        <v>50000</v>
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE EXTENSÃO</t>
+        </is>
       </c>
     </row>
     <row r="323" ht="15.75" customHeight="1" s="4">
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>POS-GRADUAÇÃO LATO SENSU</t>
-        </is>
+          <t>DIRETORIA DE EXTENSÃO</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="324" ht="15.75" customHeight="1" s="4">
-      <c r="C324" s="3" t="inlineStr">
-        <is>
-          <t>ESPECIALIZACAO</t>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>SARC - SEÇÃO DE ARTE E CULTURA</t>
         </is>
       </c>
       <c r="E324" s="3" t="n">
-        <v>51000</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="325" ht="15.75" customHeight="1" s="4">
-      <c r="C325" s="3" t="inlineStr">
-        <is>
-          <t>ESPECIALIZACAO AGROECOLOGIA</t>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>SEÇÃO DE ESTÁGIO</t>
         </is>
       </c>
       <c r="E325" s="3" t="n">
-        <v>51100</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="326" ht="15.75" customHeight="1" s="4">
-      <c r="C326" s="3" t="inlineStr">
-        <is>
-          <t>ESPECIALIZACAO DESENVOLVIMENTO WEB</t>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>RELAÇÕES INSTITUCIONAIS</t>
         </is>
       </c>
       <c r="E326" s="3" t="n">
-        <v>51200</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="327" ht="15.75" customHeight="1" s="4">
-      <c r="C327" s="3" t="inlineStr">
-        <is>
-          <t>ESPECIALIZACAO ENSINO DE MATEMATICA E FISICA</t>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>SEÇÃO DE AÇÕES COMUNITÁRIAS</t>
         </is>
       </c>
       <c r="E327" s="3" t="n">
-        <v>51300</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="328" ht="15.75" customHeight="1" s="4">
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>MESTRADO</t>
-        </is>
+          <t>SALA PROJETO PARTIU IF</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>44001</v>
       </c>
     </row>
     <row r="329" ht="15.75" customHeight="1" s="4">
-      <c r="C329" s="3" t="inlineStr">
-        <is>
-          <t>MESTRADO</t>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>SALA DA DIRETORIA DE EXTENSÃO</t>
         </is>
       </c>
       <c r="E329" s="3" t="n">
-        <v>52000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="330" ht="15.75" customHeight="1" s="4">
-      <c r="C330" s="3" t="inlineStr">
-        <is>
-          <t>MESTRADO PROFEPT</t>
-        </is>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>SALA DE REUNIÃO</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="n">
+        <v>46000</v>
       </c>
     </row>
     <row r="331" ht="15.75" customHeight="1" s="4">
-      <c r="D331" s="3" t="inlineStr">
-        <is>
-          <t>MESTRADO PROFEPT</t>
-        </is>
-      </c>
-      <c r="E331" s="3" t="n">
-        <v>52100</v>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>EMPRESA JUNIOR</t>
+        </is>
       </c>
     </row>
     <row r="332" ht="15.75" customHeight="1" s="4">
-      <c r="D332" s="3" t="inlineStr">
-        <is>
-          <t>PROFEPT - SALA DA COORDENACAO</t>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>EMPRESA JUNIOR</t>
         </is>
       </c>
       <c r="E332" s="3" t="n">
-        <v>52101</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="333" ht="15.75" customHeight="1" s="4">
-      <c r="D333" s="3" t="inlineStr">
-        <is>
-          <t>PROFEPT - SALAS DE AULA</t>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>EMPRESA JUNIOR AGROECO JR (ANTIGO ALOJAMENTO / BLOCO B / SALA 3)</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>52102</v>
+        <v>47001</v>
       </c>
     </row>
     <row r="334" ht="15.75" customHeight="1" s="4">
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>MESTRADO PROFISSIONAL NUTRICAO E PRODUCAO ANIMAL</t>
+          <t>EMPRESA JUNIOR EMCOMP (ANTIGO ALOJAMENTO / BLOCO B / SALA 4)</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
-        <v>52200</v>
+        <v>47002</v>
       </c>
     </row>
     <row r="335" ht="15.75" customHeight="1" s="4">
-      <c r="C335" s="3" t="inlineStr">
-        <is>
-          <t>MESTRADO PROFISSIONAL ALIMENTOS</t>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>TEATRO (ANTIGO ALOJAMENTO/BLOCO B/SALA 5)</t>
         </is>
       </c>
       <c r="E335" s="3" t="n">
-        <v>52300</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="336" ht="15.75" customHeight="1" s="4">
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>DOUTORADO</t>
-        </is>
-      </c>
-      <c r="E336" s="3" t="n">
-        <v>53000</v>
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE PESQUISA E POS-GRADUACAO</t>
+        </is>
       </c>
     </row>
     <row r="337" ht="15.75" customHeight="1" s="4">
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>NITTEC</t>
+          <t>DIRETORIA DE PESQUISA E POS-GRADUACAO</t>
         </is>
       </c>
       <c r="E337" s="3" t="n">
-        <v>54000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="338" ht="15.75" customHeight="1" s="4">
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>IF MAKER / NITTEC / IPCA</t>
-        </is>
-      </c>
-      <c r="E338" s="3" t="n">
-        <v>54001</v>
+          <t>POS-GRADUAÇÃO LATO SENSU</t>
+        </is>
       </c>
     </row>
     <row r="339" ht="15.75" customHeight="1" s="4">
-      <c r="B339" s="3" t="inlineStr">
-        <is>
-          <t>GERENCIA DE PESQUISA</t>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACAO</t>
         </is>
       </c>
       <c r="E339" s="3" t="n">
-        <v>55000</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="340" ht="15.75" customHeight="1" s="4">
-      <c r="A340" s="3" t="inlineStr">
-        <is>
-          <t>DIRETORIA DE DESENVOLVIMENTO INSTITUCIONAL</t>
-        </is>
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACAO AGROECOLOGIA</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>51100</v>
       </c>
     </row>
     <row r="341" ht="15.75" customHeight="1" s="4">
-      <c r="B341" s="3" t="inlineStr">
-        <is>
-          <t>DIRETORIA DE DESENVOLVIMENTO INSTITUCIONAL</t>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACAO DESENVOLVIMENTO WEB</t>
         </is>
       </c>
       <c r="E341" s="3" t="n">
-        <v>60000</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="342" ht="15.75" customHeight="1" s="4">
-      <c r="B342" s="3" t="inlineStr">
-        <is>
-          <t>PREFEITURA</t>
-        </is>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACAO ENSINO DE MATEMATICA E FISICA</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>51300</v>
       </c>
     </row>
     <row r="343" ht="15.75" customHeight="1" s="4">
-      <c r="C343" s="3" t="inlineStr">
-        <is>
-          <t>PREFEITURA</t>
-        </is>
-      </c>
-      <c r="E343" s="3" t="n">
-        <v>61000</v>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>MESTRADO</t>
+        </is>
       </c>
     </row>
     <row r="344" ht="15.75" customHeight="1" s="4">
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>VIGILANCIA</t>
+          <t>MESTRADO</t>
         </is>
       </c>
       <c r="E344" s="3" t="n">
-        <v>61100</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="345" ht="15.75" customHeight="1" s="4">
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>RECICLAGEM</t>
-        </is>
-      </c>
-      <c r="E345" s="3" t="n">
-        <v>61200</v>
+          <t>MESTRADO PROFEPT</t>
+        </is>
       </c>
     </row>
     <row r="346" ht="15.75" customHeight="1" s="4">
-      <c r="C346" s="3" t="inlineStr">
-        <is>
-          <t>SEÇÃO DE SERVICO DE APOIO</t>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>MESTRADO PROFEPT</t>
         </is>
       </c>
       <c r="E346" s="3" t="n">
-        <v>61300</v>
+        <v>52100</v>
       </c>
     </row>
     <row r="347" ht="15.75" customHeight="1" s="4">
-      <c r="C347" s="3" t="inlineStr">
-        <is>
-          <t>PREFEITURA - ESTACAO DE TRATAMENTO DE AGUA</t>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>PROFEPT - SALA DA COORDENACAO</t>
         </is>
       </c>
       <c r="E347" s="3" t="n">
-        <v>61400</v>
+        <v>52101</v>
       </c>
     </row>
     <row r="348" ht="15.75" customHeight="1" s="4">
-      <c r="C348" s="3" t="inlineStr">
-        <is>
-          <t>PREFEITURA - MANUTEN. E DEPOS. MATER.CONSTRU</t>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>PROFEPT - SALAS DE AULA</t>
         </is>
       </c>
       <c r="E348" s="3" t="n">
-        <v>61401</v>
+        <v>52102</v>
       </c>
     </row>
     <row r="349" ht="15.75" customHeight="1" s="4">
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>PREFEITURA - SERRALHERIA</t>
+          <t>MESTRADO PROFISSIONAL NUTRICAO E PRODUCAO ANIMAL</t>
         </is>
       </c>
       <c r="E349" s="3" t="n">
-        <v>61402</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="350" ht="15.75" customHeight="1" s="4">
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>PREFEITURA - CARPINTARIA</t>
+          <t>MESTRADO PROFISSIONAL ALIMENTOS</t>
         </is>
       </c>
       <c r="E350" s="3" t="n">
-        <v>61403</v>
+        <v>52300</v>
       </c>
     </row>
     <row r="351" ht="15.75" customHeight="1" s="4">
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>COORDENACAO GERAL DE PRODUCAO</t>
-        </is>
+          <t>DOUTORADO</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="n">
+        <v>53000</v>
       </c>
     </row>
     <row r="352" ht="15.75" customHeight="1" s="4">
-      <c r="C352" s="3" t="inlineStr">
-        <is>
-          <t>COORDENACAO GERAL DE PRODUCAO</t>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>NITTEC</t>
         </is>
       </c>
       <c r="E352" s="3" t="n">
-        <v>62000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="353" ht="15.75" customHeight="1" s="4">
-      <c r="C353" s="3" t="inlineStr">
-        <is>
-          <t>MECANIZACAO AGRICOLA</t>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>IF MAKER / NITTEC / IPCA</t>
         </is>
       </c>
       <c r="E353" s="3" t="n">
-        <v>62100</v>
+        <v>54001</v>
       </c>
     </row>
     <row r="354" ht="15.75" customHeight="1" s="4">
-      <c r="C354" s="3" t="inlineStr">
-        <is>
-          <t>POSTO DE VENDAS</t>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>GERENCIA DE PESQUISA</t>
         </is>
       </c>
       <c r="E354" s="3" t="n">
-        <v>62200</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="355" ht="15.75" customHeight="1" s="4">
-      <c r="C355" s="3" t="inlineStr">
-        <is>
-          <t>SECAO DE PROJETOS E PRODUCAO AGROINDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="E355" s="3" t="n">
-        <v>62300</v>
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE DESENVOLVIMENTO INSTITUCIONAL</t>
+        </is>
       </c>
     </row>
     <row r="356" ht="15.75" customHeight="1" s="4">
-      <c r="C356" s="3" t="inlineStr">
-        <is>
-          <t>PADARIA</t>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE DESENVOLVIMENTO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="E356" s="3" t="n">
-        <v>62301</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="357" ht="15.75" customHeight="1" s="4">
-      <c r="C357" s="3" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
-      </c>
-      <c r="E357" s="3" t="n">
-        <v>62302</v>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>PREFEITURA</t>
+        </is>
       </c>
     </row>
     <row r="358" ht="15.75" customHeight="1" s="4">
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>CARNES</t>
+          <t>PREFEITURA</t>
         </is>
       </c>
       <c r="E358" s="3" t="n">
-        <v>62303</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="359" ht="15.75" customHeight="1" s="4">
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>INDUSTRIAS RURAIS</t>
+          <t>VIGILANCIA</t>
         </is>
       </c>
       <c r="E359" s="3" t="n">
-        <v>62304</v>
+        <v>61100</v>
       </c>
     </row>
     <row r="360" ht="15.75" customHeight="1" s="4">
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>AGROINDUSTRIA - ESCRITORIO E ALMOXARIFADO</t>
+          <t>RECICLAGEM</t>
         </is>
       </c>
       <c r="E360" s="3" t="n">
-        <v>62305</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="361" ht="15.75" customHeight="1" s="4">
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>LATICINIO</t>
+          <t>SEÇÃO DE SERVICO DE APOIO</t>
         </is>
       </c>
       <c r="E361" s="3" t="n">
-        <v>62306</v>
+        <v>61300</v>
       </c>
     </row>
     <row r="362" ht="15.75" customHeight="1" s="4">
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>CALDEIRA</t>
+          <t>PREFEITURA - ESTACAO DE TRATAMENTO DE AGUA</t>
         </is>
       </c>
       <c r="E362" s="3" t="n">
-        <v>62307</v>
+        <v>61400</v>
       </c>
     </row>
     <row r="363" ht="15.75" customHeight="1" s="4">
-      <c r="B363" s="3" t="inlineStr">
-        <is>
-          <t>GERENCIA DE TECNOLOGIA DA INFORMACAO</t>
-        </is>
+      <c r="C363" s="3" t="inlineStr">
+        <is>
+          <t>PREFEITURA - MANUTEN. E DEPOS. MATER.CONSTRU</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="n">
+        <v>61401</v>
       </c>
     </row>
     <row r="364" ht="15.75" customHeight="1" s="4">
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA DE TECNOLOGIA DA INFORMACAO</t>
+          <t>PREFEITURA - SERRALHERIA</t>
         </is>
       </c>
       <c r="E364" s="3" t="n">
-        <v>63000</v>
+        <v>61402</v>
       </c>
     </row>
     <row r="365" ht="15.75" customHeight="1" s="4">
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>TI - DATACENTER</t>
+          <t>PREFEITURA - CARPINTARIA</t>
         </is>
       </c>
       <c r="E365" s="3" t="n">
-        <v>63001</v>
+        <v>61403</v>
       </c>
     </row>
     <row r="366" ht="15.75" customHeight="1" s="4">
-      <c r="A366" s="3" t="inlineStr">
-        <is>
-          <t>DIRETOR GERAL</t>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>COORDENACAO GERAL DE PRODUCAO</t>
         </is>
       </c>
     </row>
     <row r="367" ht="15.75" customHeight="1" s="4">
-      <c r="B367" s="3" t="inlineStr">
-        <is>
-          <t>DIRETOR GERAL</t>
+      <c r="C367" s="3" t="inlineStr">
+        <is>
+          <t>COORDENACAO GERAL DE PRODUCAO</t>
         </is>
       </c>
       <c r="E367" s="3" t="n">
-        <v>70000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="368" ht="15.75" customHeight="1" s="4">
-      <c r="B368" s="3" t="inlineStr">
-        <is>
-          <t>EMPRESTIMO DE BENS</t>
+      <c r="C368" s="3" t="inlineStr">
+        <is>
+          <t>MECANIZACAO AGRICOLA</t>
         </is>
       </c>
       <c r="E368" s="3" t="n">
-        <v>70001</v>
+        <v>62100</v>
       </c>
     </row>
     <row r="369" ht="15.75" customHeight="1" s="4">
-      <c r="B369" s="3" t="inlineStr">
-        <is>
-          <t>AUDITORIA INTERNA</t>
+      <c r="C369" s="3" t="inlineStr">
+        <is>
+          <t>POSTO DE VENDAS</t>
         </is>
       </c>
       <c r="E369" s="3" t="n">
-        <v>70002</v>
+        <v>62200</v>
       </c>
     </row>
     <row r="370" ht="15.75" customHeight="1" s="4">
-      <c r="B370" s="3" t="inlineStr">
-        <is>
-          <t>ARQUIVO MORTO / GERAL</t>
+      <c r="C370" s="3" t="inlineStr">
+        <is>
+          <t>SECAO DE PROJETOS E PRODUCAO AGROINDUSTRIAL</t>
         </is>
       </c>
       <c r="E370" s="3" t="n">
-        <v>70003</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" s="4">
-      <c r="B371" s="3" t="inlineStr">
-        <is>
-          <t>CESSAO DE BENS</t>
+      <c r="C371" s="3" t="inlineStr">
+        <is>
+          <t>PADARIA</t>
         </is>
       </c>
       <c r="E371" s="3" t="n">
-        <v>70004</v>
+        <v>62301</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" s="4">
-      <c r="B372" s="3" t="inlineStr">
-        <is>
-          <t>SALAO NOBRE</t>
+      <c r="C372" s="3" t="inlineStr">
+        <is>
+          <t>FRUTAS</t>
         </is>
       </c>
       <c r="E372" s="3" t="n">
-        <v>70005</v>
+        <v>62302</v>
       </c>
     </row>
     <row r="373" ht="15.75" customHeight="1" s="4">
-      <c r="B373" s="3" t="inlineStr">
-        <is>
-          <t>GABINETE</t>
+      <c r="C373" s="3" t="inlineStr">
+        <is>
+          <t>CARNES</t>
         </is>
       </c>
       <c r="E373" s="3" t="n">
-        <v>70006</v>
+        <v>62303</v>
       </c>
     </row>
     <row r="374" ht="15.75" customHeight="1" s="4">
-      <c r="B374" s="3" t="inlineStr">
-        <is>
-          <t>GESTAO DE PESSOAS</t>
+      <c r="C374" s="3" t="inlineStr">
+        <is>
+          <t>INDUSTRIAS RURAIS</t>
         </is>
       </c>
       <c r="E374" s="3" t="n">
-        <v>70007</v>
+        <v>62304</v>
       </c>
     </row>
     <row r="375" ht="15.75" customHeight="1" s="4">
-      <c r="B375" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO</t>
-        </is>
+      <c r="C375" s="3" t="inlineStr">
+        <is>
+          <t>AGROINDUSTRIA - ESCRITORIO E ALMOXARIFADO</t>
+        </is>
+      </c>
+      <c r="E375" s="3" t="n">
+        <v>62305</v>
       </c>
     </row>
     <row r="376" ht="15.75" customHeight="1" s="4">
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>FUNDACAO - REFEITORIO</t>
+          <t>LATICINIO</t>
         </is>
       </c>
       <c r="E376" s="3" t="n">
-        <v>70009</v>
+        <v>62306</v>
       </c>
     </row>
     <row r="377" ht="15.75" customHeight="1" s="4">
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>FUNDACAO - DORMITORIO 1</t>
+          <t>CALDEIRA</t>
         </is>
       </c>
       <c r="E377" s="3" t="n">
-        <v>70011</v>
+        <v>62307</v>
       </c>
     </row>
     <row r="378" ht="15.75" customHeight="1" s="4">
-      <c r="C378" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - DORMITORIO 2</t>
-        </is>
-      </c>
-      <c r="E378" s="3" t="n">
-        <v>70012</v>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>GERENCIA DE TECNOLOGIA DA INFORMACAO</t>
+        </is>
       </c>
     </row>
     <row r="379" ht="15.75" customHeight="1" s="4">
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>FUNDACAO - DORMITORIO 3</t>
+          <t>GERENCIA DE TECNOLOGIA DA INFORMACAO</t>
         </is>
       </c>
       <c r="E379" s="3" t="n">
-        <v>70013</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="380" ht="15.75" customHeight="1" s="4">
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>FUNDACAO - DORMITORIO 4</t>
+          <t>TI - DATACENTER</t>
         </is>
       </c>
       <c r="E380" s="3" t="n">
-        <v>70014</v>
+        <v>63001</v>
       </c>
     </row>
     <row r="381" ht="15.75" customHeight="1" s="4">
-      <c r="C381" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - DORMITORIO 5</t>
-        </is>
-      </c>
-      <c r="E381" s="3" t="n">
-        <v>70015</v>
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>DIRETOR GERAL</t>
+        </is>
       </c>
     </row>
     <row r="382" ht="15.75" customHeight="1" s="4">
-      <c r="C382" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - DORMITORIO 6</t>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>DIRETOR GERAL</t>
         </is>
       </c>
       <c r="E382" s="3" t="n">
-        <v>70016</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="383" ht="15.75" customHeight="1" s="4">
-      <c r="C383" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - DORMITORIO 7</t>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>EMPRESTIMO DE BENS</t>
         </is>
       </c>
       <c r="E383" s="3" t="n">
-        <v>70017</v>
+        <v>70001</v>
       </c>
     </row>
     <row r="384" ht="15.75" customHeight="1" s="4">
-      <c r="C384" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - DORMITORIO 8</t>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>AUDITORIA INTERNA</t>
         </is>
       </c>
       <c r="E384" s="3" t="n">
-        <v>70018</v>
+        <v>70002</v>
       </c>
     </row>
     <row r="385" ht="15.75" customHeight="1" s="4">
-      <c r="C385" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - DORMITORIO 9</t>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>ARQUIVO MORTO / GERAL</t>
         </is>
       </c>
       <c r="E385" s="3" t="n">
-        <v>70019</v>
+        <v>70003</v>
       </c>
     </row>
     <row r="386" ht="15.75" customHeight="1" s="4">
-      <c r="C386" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - DORMITORIO 10</t>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>CESSAO DE BENS</t>
         </is>
       </c>
       <c r="E386" s="3" t="n">
-        <v>70020</v>
+        <v>70004</v>
       </c>
     </row>
     <row r="387" ht="15.75" customHeight="1" s="4">
-      <c r="C387" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - DORMITORIO 11</t>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>SALAO NOBRE</t>
         </is>
       </c>
       <c r="E387" s="3" t="n">
-        <v>70021</v>
+        <v>70005</v>
       </c>
     </row>
     <row r="388" ht="15.75" customHeight="1" s="4">
-      <c r="C388" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - HALL SEGUNDO ANDAR</t>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>GABINETE</t>
         </is>
       </c>
       <c r="E388" s="3" t="n">
-        <v>70022</v>
+        <v>70006</v>
       </c>
     </row>
     <row r="389" ht="15.75" customHeight="1" s="4">
-      <c r="C389" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - SALA SEGUNDO ANDAR</t>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>GESTAO DE PESSOAS</t>
         </is>
       </c>
       <c r="E389" s="3" t="n">
-        <v>70023</v>
+        <v>70007</v>
       </c>
     </row>
     <row r="390" ht="15.75" customHeight="1" s="4">
-      <c r="C390" s="3" t="inlineStr">
-        <is>
-          <t>FUNDACAO - ANFITEATRO JARBAS FURTADO</t>
-        </is>
-      </c>
-      <c r="E390" s="3" t="n">
-        <v>70010</v>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>FUNDACAO</t>
+        </is>
       </c>
     </row>
     <row r="391" ht="15.75" customHeight="1" s="4">
-      <c r="B391" s="3" t="inlineStr">
-        <is>
-          <t>CENTRO DE VIVENCIA / CANTINA</t>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t>FUNDACAO - REFEITORIO</t>
         </is>
       </c>
       <c r="E391" s="3" t="n">
-        <v>70024</v>
+        <v>70009</v>
       </c>
     </row>
     <row r="392" ht="15.75" customHeight="1" s="4">
-      <c r="B392" s="3" t="inlineStr">
-        <is>
-          <t>ALOJAMENTO - BLOCO C</t>
-        </is>
+      <c r="C392" s="3" t="inlineStr">
+        <is>
+          <t>FUNDACAO - DORMITORIO 1</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="n">
+        <v>70011</v>
       </c>
     </row>
     <row r="393" ht="15.75" customHeight="1" s="4">
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO C - QUARTO 1</t>
+          <t>FUNDACAO - DORMITORIO 2</t>
         </is>
       </c>
       <c r="E393" s="3" t="n">
-        <v>70025</v>
+        <v>70012</v>
       </c>
     </row>
     <row r="394" ht="15.75" customHeight="1" s="4">
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO C - QUARTO 2</t>
+          <t>FUNDACAO - DORMITORIO 3</t>
         </is>
       </c>
       <c r="E394" s="3" t="n">
-        <v>70026</v>
+        <v>70013</v>
       </c>
     </row>
     <row r="395" ht="15.75" customHeight="1" s="4">
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO C - QUARTO 3</t>
+          <t>FUNDACAO - DORMITORIO 4</t>
         </is>
       </c>
       <c r="E395" s="3" t="n">
-        <v>70027</v>
+        <v>70014</v>
       </c>
     </row>
     <row r="396" ht="15.75" customHeight="1" s="4">
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO C - QUARTO 4</t>
+          <t>FUNDACAO - DORMITORIO 5</t>
         </is>
       </c>
       <c r="E396" s="3" t="n">
-        <v>70028</v>
+        <v>70015</v>
       </c>
     </row>
     <row r="397" ht="15.75" customHeight="1" s="4">
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO C - QUARTO 5</t>
+          <t>FUNDACAO - DORMITORIO 6</t>
         </is>
       </c>
       <c r="E397" s="3" t="n">
-        <v>70029</v>
+        <v>70016</v>
       </c>
     </row>
     <row r="398" ht="15.75" customHeight="1" s="4">
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO C - QUARTO 6</t>
+          <t>FUNDACAO - DORMITORIO 7</t>
         </is>
       </c>
       <c r="E398" s="3" t="n">
-        <v>70030</v>
+        <v>70017</v>
       </c>
     </row>
     <row r="399" ht="15.75" customHeight="1" s="4">
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO C - QUARTO 7</t>
+          <t>FUNDACAO - DORMITORIO 8</t>
         </is>
       </c>
       <c r="E399" s="3" t="n">
-        <v>70031</v>
+        <v>70018</v>
       </c>
     </row>
     <row r="400" ht="15.75" customHeight="1" s="4">
-      <c r="B400" s="3" t="inlineStr">
-        <is>
-          <t>ALOJAMENTO - BLOCO D</t>
-        </is>
+      <c r="C400" s="3" t="inlineStr">
+        <is>
+          <t>FUNDACAO - DORMITORIO 9</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="n">
+        <v>70019</v>
       </c>
     </row>
     <row r="401" ht="15.75" customHeight="1" s="4">
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO D - QUARTO 1</t>
+          <t>FUNDACAO - DORMITORIO 10</t>
         </is>
       </c>
       <c r="E401" s="3" t="n">
-        <v>70032</v>
+        <v>70020</v>
       </c>
     </row>
     <row r="402" ht="15.75" customHeight="1" s="4">
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO D - QUARTO 2</t>
+          <t>FUNDACAO - DORMITORIO 11</t>
         </is>
       </c>
       <c r="E402" s="3" t="n">
-        <v>70033</v>
+        <v>70021</v>
       </c>
     </row>
     <row r="403" ht="15.75" customHeight="1" s="4">
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO D - QUARTO 3</t>
+          <t>FUNDACAO - HALL SEGUNDO ANDAR</t>
         </is>
       </c>
       <c r="E403" s="3" t="n">
-        <v>70034</v>
+        <v>70022</v>
       </c>
     </row>
     <row r="404" ht="15.75" customHeight="1" s="4">
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO D - QUARTO 4</t>
+          <t>FUNDACAO - SALA SEGUNDO ANDAR</t>
         </is>
       </c>
       <c r="E404" s="3" t="n">
-        <v>70035</v>
+        <v>70023</v>
       </c>
     </row>
     <row r="405" ht="15.75" customHeight="1" s="4">
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - BLOCO D - QUARTO 5</t>
+          <t>FUNDACAO - ANFITEATRO JARBAS FURTADO</t>
         </is>
       </c>
       <c r="E405" s="3" t="n">
-        <v>70036</v>
+        <v>70010</v>
       </c>
     </row>
     <row r="406" ht="15.75" customHeight="1" s="4">
-      <c r="C406" s="3" t="inlineStr">
-        <is>
-          <t>ALOJAMENTO - BLOCO D - QUARTO 6</t>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>CENTRO DE VIVENCIA / CANTINA</t>
         </is>
       </c>
       <c r="E406" s="3" t="n">
-        <v>70037</v>
+        <v>70024</v>
       </c>
     </row>
     <row r="407" ht="15.75" customHeight="1" s="4">
-      <c r="C407" s="3" t="inlineStr">
-        <is>
-          <t>ALOJAMENTO - BLOCO D - QUARTO 7</t>
-        </is>
-      </c>
-      <c r="E407" s="3" t="n">
-        <v>70038</v>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO C</t>
+        </is>
       </c>
     </row>
     <row r="408" ht="15.75" customHeight="1" s="4">
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>ALOJAMENTO - GALPAO / DEPOSITO</t>
+          <t>ALOJAMENTO - BLOCO C - QUARTO 1</t>
         </is>
       </c>
       <c r="E408" s="3" t="n">
-        <v>70039</v>
+        <v>70025</v>
       </c>
     </row>
     <row r="409" ht="15.75" customHeight="1" s="4">
-      <c r="B409" s="3" t="inlineStr">
-        <is>
-          <t>COMUNICACAO</t>
-        </is>
+      <c r="C409" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO C - QUARTO 2</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="n">
+        <v>70026</v>
       </c>
     </row>
     <row r="410" ht="15.75" customHeight="1" s="4">
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>COMUNICACAO</t>
+          <t>ALOJAMENTO - BLOCO C - QUARTO 3</t>
         </is>
       </c>
       <c r="E410" s="3" t="n">
-        <v>71000</v>
+        <v>70027</v>
       </c>
     </row>
     <row r="411" ht="15.75" customHeight="1" s="4">
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>SALA DA COMUNICACAO - FUNDACAO</t>
+          <t>ALOJAMENTO - BLOCO C - QUARTO 4</t>
         </is>
       </c>
       <c r="E411" s="3" t="n">
-        <v>71002</v>
+        <v>70028</v>
       </c>
     </row>
     <row r="412" ht="15.75" customHeight="1" s="4">
       <c r="C412" s="3" t="inlineStr">
         <is>
+          <t>ALOJAMENTO - BLOCO C - QUARTO 5</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="n">
+        <v>70029</v>
+      </c>
+    </row>
+    <row r="413" ht="15.75" customHeight="1" s="4">
+      <c r="C413" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO C - QUARTO 6</t>
+        </is>
+      </c>
+      <c r="E413" s="3" t="n">
+        <v>70030</v>
+      </c>
+    </row>
+    <row r="414" ht="15.75" customHeight="1" s="4">
+      <c r="C414" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO C - QUARTO 7</t>
+        </is>
+      </c>
+      <c r="E414" s="3" t="n">
+        <v>70031</v>
+      </c>
+    </row>
+    <row r="415" ht="15.75" customHeight="1" s="4">
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO D</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="15.75" customHeight="1" s="4">
+      <c r="C416" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO D - QUARTO 1</t>
+        </is>
+      </c>
+      <c r="E416" s="3" t="n">
+        <v>70032</v>
+      </c>
+    </row>
+    <row r="417" ht="15.75" customHeight="1" s="4">
+      <c r="C417" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO D - QUARTO 2</t>
+        </is>
+      </c>
+      <c r="E417" s="3" t="n">
+        <v>70033</v>
+      </c>
+    </row>
+    <row r="418" ht="15.75" customHeight="1" s="4">
+      <c r="C418" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO D - QUARTO 3</t>
+        </is>
+      </c>
+      <c r="E418" s="3" t="n">
+        <v>70034</v>
+      </c>
+    </row>
+    <row r="419" ht="15.75" customHeight="1" s="4">
+      <c r="C419" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO D - QUARTO 4</t>
+        </is>
+      </c>
+      <c r="E419" s="3" t="n">
+        <v>70035</v>
+      </c>
+    </row>
+    <row r="420" ht="15.75" customHeight="1" s="4">
+      <c r="C420" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO D - QUARTO 5</t>
+        </is>
+      </c>
+      <c r="E420" s="3" t="n">
+        <v>70036</v>
+      </c>
+    </row>
+    <row r="421" ht="15.75" customHeight="1" s="4">
+      <c r="C421" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO D - QUARTO 6</t>
+        </is>
+      </c>
+      <c r="E421" s="3" t="n">
+        <v>70037</v>
+      </c>
+    </row>
+    <row r="422" ht="15.75" customHeight="1" s="4">
+      <c r="C422" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - BLOCO D - QUARTO 7</t>
+        </is>
+      </c>
+      <c r="E422" s="3" t="n">
+        <v>70038</v>
+      </c>
+    </row>
+    <row r="423" ht="15.75" customHeight="1" s="4">
+      <c r="C423" s="3" t="inlineStr">
+        <is>
+          <t>ALOJAMENTO - GALPAO / DEPOSITO</t>
+        </is>
+      </c>
+      <c r="E423" s="3" t="n">
+        <v>70039</v>
+      </c>
+    </row>
+    <row r="424" ht="15.75" customHeight="1" s="4">
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>SALA WEB RADIO (ALOJAMENTO / BLOCO B / SALA 1)</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>70040</v>
+      </c>
+    </row>
+    <row r="425" ht="15.75" customHeight="1" s="4">
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>CAPELA / IGREJINHA</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>70041</v>
+      </c>
+    </row>
+    <row r="426" ht="15.75" customHeight="1" s="4">
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>COMUNICACAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="15.75" customHeight="1" s="4">
+      <c r="C427" s="3" t="inlineStr">
+        <is>
+          <t>COMUNICACAO</t>
+        </is>
+      </c>
+      <c r="E427" s="3" t="n">
+        <v>71000</v>
+      </c>
+    </row>
+    <row r="428" ht="15.75" customHeight="1" s="4">
+      <c r="C428" s="3" t="inlineStr">
+        <is>
+          <t>SALA DA COMUNICACAO - FUNDACAO</t>
+        </is>
+      </c>
+      <c r="E428" s="3" t="n">
+        <v>71002</v>
+      </c>
+    </row>
+    <row r="429" ht="15.75" customHeight="1" s="4">
+      <c r="C429" s="3" t="inlineStr">
+        <is>
           <t>SALA DA COMUNICACAO - PREDIO ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="E412" s="3" t="n">
+      <c r="E429" s="3" t="n">
         <v>71001</v>
       </c>
     </row>
-    <row r="413" ht="15.75" customHeight="1" s="4"/>
-    <row r="414" ht="15.75" customHeight="1" s="4"/>
-    <row r="415" ht="15.75" customHeight="1" s="4"/>
-    <row r="416" ht="15.75" customHeight="1" s="4"/>
-    <row r="417" ht="15.75" customHeight="1" s="4"/>
-    <row r="418" ht="15.75" customHeight="1" s="4"/>
-    <row r="419" ht="15.75" customHeight="1" s="4"/>
-    <row r="420" ht="15.75" customHeight="1" s="4"/>
-    <row r="421" ht="15.75" customHeight="1" s="4"/>
-    <row r="422" ht="15.75" customHeight="1" s="4"/>
-    <row r="423" ht="15.75" customHeight="1" s="4"/>
-    <row r="424" ht="15.75" customHeight="1" s="4"/>
-    <row r="425" ht="15.75" customHeight="1" s="4"/>
-    <row r="426" ht="15.75" customHeight="1" s="4"/>
-    <row r="427" ht="15.75" customHeight="1" s="4"/>
-    <row r="428" ht="15.75" customHeight="1" s="4"/>
-    <row r="429" ht="15.75" customHeight="1" s="4"/>
     <row r="430" ht="15.75" customHeight="1" s="4"/>
     <row r="431" ht="15.75" customHeight="1" s="4"/>
     <row r="432" ht="15.75" customHeight="1" s="4"/>

--- a/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
+++ b/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
@@ -614,12 +614,12 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="4">
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>PREDIO CENTRAL - SALA DE TELECOM</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="0" t="n">
         <v>20023</v>
       </c>
     </row>
@@ -1089,19 +1089,19 @@
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="4">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>DEPARTAMENTOS</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="4">
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>DEPARTAMENTOS</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="0" t="n">
         <v>26000</v>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
     <row r="211" ht="15.75" customHeight="1" s="4">
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>DMAFE - IPCA - LAB PESQUISA ENS DE MAT - LAPEM</t>
+          <t>DEMAFE - IPCA - LAB PESQUISA ENS DE MAT - LAPEM</t>
         </is>
       </c>
       <c r="E211" s="3" t="n">
@@ -2581,12 +2581,12 @@
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1" s="4">
-      <c r="C229" t="inlineStr">
+      <c r="C229" s="0" t="inlineStr">
         <is>
           <t>DZO - PREDIO DA ZOOTECNIA - VARANDA E CORREDORES</t>
         </is>
       </c>
-      <c r="E229" t="n">
+      <c r="E229" s="0" t="n">
         <v>26716</v>
       </c>
     </row>
@@ -2811,82 +2811,82 @@
       </c>
     </row>
     <row r="252" ht="15.75" customHeight="1" s="4">
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="0" t="inlineStr">
         <is>
           <t>DZO - GALPAO EXPERIMENTAL DE BOVINOCULTURA</t>
         </is>
       </c>
-      <c r="E252" t="n">
+      <c r="E252" s="0" t="n">
         <v>26738</v>
       </c>
     </row>
     <row r="253" ht="15.75" customHeight="1" s="4">
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="0" t="inlineStr">
         <is>
           <t>DZO - CUNICULTURA - COELHOS</t>
         </is>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" s="0" t="n">
         <v>26739</v>
       </c>
     </row>
     <row r="254" ht="15.75" customHeight="1" s="4">
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="0" t="inlineStr">
         <is>
           <t>DZO - LABORATORIO OVINOCAPRINOCULTURA</t>
         </is>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" s="0" t="n">
         <v>26740</v>
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1" s="4">
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="0" t="inlineStr">
         <is>
           <t>DZO - FRANGO - CORTE</t>
         </is>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" s="0" t="n">
         <v>26741</v>
       </c>
     </row>
     <row r="256" ht="15.75" customHeight="1" s="4">
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="0" t="inlineStr">
         <is>
           <t>DZO - CAPRINOCULTURA</t>
         </is>
       </c>
-      <c r="E256" t="n">
+      <c r="E256" s="0" t="n">
         <v>26742</v>
       </c>
     </row>
     <row r="257" ht="15.75" customHeight="1" s="4">
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="0" t="inlineStr">
         <is>
           <t>DZO - DEPOSITOS E SALA DE APOIO LAB OVINOCAPRINO</t>
         </is>
       </c>
-      <c r="E257" t="n">
+      <c r="E257" s="0" t="n">
         <v>26743</v>
       </c>
     </row>
     <row r="258" ht="15.75" customHeight="1" s="4">
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="0" t="inlineStr">
         <is>
           <t>DZO - APICULTURA</t>
         </is>
       </c>
-      <c r="E258" t="n">
+      <c r="E258" s="0" t="n">
         <v>26744</v>
       </c>
     </row>
     <row r="259" ht="15.75" customHeight="1" s="4">
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="0" t="inlineStr">
         <is>
           <t>DZO - SEMOVENTES</t>
         </is>
       </c>
-      <c r="E259" t="n">
+      <c r="E259" s="0" t="n">
         <v>26745</v>
       </c>
     </row>
@@ -3223,12 +3223,12 @@
       </c>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="4">
-      <c r="B295" t="inlineStr">
+      <c r="B295" s="0" t="inlineStr">
         <is>
           <t>COORDENACAO GERAL DE ADMINISTRACAO E FINANCAS</t>
         </is>
       </c>
-      <c r="E295" t="n">
+      <c r="E295" s="0" t="n">
         <v>31000</v>
       </c>
     </row>
@@ -3387,22 +3387,22 @@
       </c>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="4">
-      <c r="C312" t="inlineStr">
+      <c r="C312" s="0" t="inlineStr">
         <is>
           <t>PATRIMONIO - GALPAO 3 - IRRECUPERAVEL/ANTIECONOMIC</t>
         </is>
       </c>
-      <c r="E312" t="n">
+      <c r="E312" s="0" t="n">
         <v>31212</v>
       </c>
     </row>
     <row r="313" ht="15.75" customHeight="1" s="4">
-      <c r="C313" t="inlineStr">
+      <c r="C313" s="0" t="inlineStr">
         <is>
           <t>PATRIMONIO - GALPAO 3</t>
         </is>
       </c>
-      <c r="E313" t="n">
+      <c r="E313" s="0" t="n">
         <v>31213</v>
       </c>
     </row>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="424" ht="15.75" customHeight="1" s="4">
-      <c r="B424" t="inlineStr">
+      <c r="B424" s="0" t="inlineStr">
         <is>
           <t>SALA WEB RADIO (ALOJAMENTO / BLOCO B / SALA 1)</t>
         </is>
       </c>
-      <c r="E424" t="n">
+      <c r="E424" s="0" t="n">
         <v>70040</v>
       </c>
     </row>
     <row r="425" ht="15.75" customHeight="1" s="4">
-      <c r="B425" t="inlineStr">
+      <c r="B425" s="0" t="inlineStr">
         <is>
           <t>CAPELA / IGREJINHA</t>
         </is>
       </c>
-      <c r="E425" t="n">
+      <c r="E425" s="0" t="n">
         <v>70041</v>
       </c>
     </row>

--- a/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
+++ b/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
@@ -2209,7 +2209,7 @@
     <row r="191" ht="15.75" customHeight="1" s="4">
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - DEP. ACADEMICO DE MATEMATICA E FISICA</t>
+          <t>DMAFE - DEP. ACADEMICO DE MATEMATICA E FISICA</t>
         </is>
       </c>
       <c r="E191" s="3" t="n">
@@ -2219,7 +2219,7 @@
     <row r="192" ht="15.75" customHeight="1" s="4">
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - LABORATORIO DE FISICA</t>
+          <t>DMAFE - LABORATORIO DE FISICA</t>
         </is>
       </c>
       <c r="E192" s="3" t="n">
@@ -2229,7 +2229,7 @@
     <row r="193" ht="15.75" customHeight="1" s="4">
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - LABORATORIO DE INFORMÁTICA</t>
+          <t>DMAFE - LABORATORIO DE INFORMÁTICA</t>
         </is>
       </c>
       <c r="E193" s="3" t="n">
@@ -2239,7 +2239,7 @@
     <row r="194" ht="15.75" customHeight="1" s="4">
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - LABORATÓRIO DE MATEMÁTICA</t>
+          <t>DMAFE - LABORATÓRIO DE MATEMÁTICA</t>
         </is>
       </c>
       <c r="E194" s="3" t="n">
@@ -2249,7 +2249,7 @@
     <row r="195" ht="15.75" customHeight="1" s="4">
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2</t>
+          <t>DMAFE - SALA DOS PROFESSORES 2</t>
         </is>
       </c>
       <c r="E195" s="3" t="n">
@@ -2259,7 +2259,7 @@
     <row r="196" ht="15.75" customHeight="1" s="4">
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 1</t>
+          <t>DMAFE - SALA DOS PROFESSORES 2 - GABINETE 1</t>
         </is>
       </c>
       <c r="E196" s="3" t="n">
@@ -2269,7 +2269,7 @@
     <row r="197" ht="15.75" customHeight="1" s="4">
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 2</t>
+          <t>DMAFE - SALA DOS PROFESSORES 2 - GABINETE 2</t>
         </is>
       </c>
       <c r="E197" s="3" t="n">
@@ -2279,7 +2279,7 @@
     <row r="198" ht="15.75" customHeight="1" s="4">
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 3</t>
+          <t>DMAFE - SALA DOS PROFESSORES 2 - GABINETE 3</t>
         </is>
       </c>
       <c r="E198" s="3" t="n">
@@ -2289,7 +2289,7 @@
     <row r="199" ht="15.75" customHeight="1" s="4">
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE 4</t>
+          <t>DMAFE - SALA DOS PROFESSORES 2 - GABINETE 4</t>
         </is>
       </c>
       <c r="E199" s="3" t="n">
@@ -2299,7 +2299,7 @@
     <row r="200" ht="15.75" customHeight="1" s="4">
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 2 - GABINETE REUNIÃO</t>
+          <t>DMAFE - SALA DOS PROFESSORES 2 - GABINETE REUNIÃO</t>
         </is>
       </c>
       <c r="E200" s="3" t="n">
@@ -2309,7 +2309,7 @@
     <row r="201" ht="15.75" customHeight="1" s="4">
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3</t>
+          <t>DMAFE - SALA DOS PROFESSORES 3</t>
         </is>
       </c>
       <c r="E201" s="3" t="n">
@@ -2319,7 +2319,7 @@
     <row r="202" ht="15.75" customHeight="1" s="4">
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 1</t>
+          <t>DMAFE - SALA DOS PROFESSORES 3 - GABINETE 1</t>
         </is>
       </c>
       <c r="E202" s="3" t="n">
@@ -2329,7 +2329,7 @@
     <row r="203" ht="15.75" customHeight="1" s="4">
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 2</t>
+          <t>DMAFE - SALA DOS PROFESSORES 3 - GABINETE 2</t>
         </is>
       </c>
       <c r="E203" s="3" t="n">
@@ -2339,7 +2339,7 @@
     <row r="204" ht="15.75" customHeight="1" s="4">
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 3</t>
+          <t>DMAFE - SALA DOS PROFESSORES 3 - GABINETE 3</t>
         </is>
       </c>
       <c r="E204" s="3" t="n">
@@ -2349,7 +2349,7 @@
     <row r="205" ht="15.75" customHeight="1" s="4">
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 4</t>
+          <t>DMAFE - SALA DOS PROFESSORES 3 - GABINETE 4</t>
         </is>
       </c>
       <c r="E205" s="3" t="n">
@@ -2359,7 +2359,7 @@
     <row r="206" ht="15.75" customHeight="1" s="4">
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 5</t>
+          <t>DMAFE - SALA DOS PROFESSORES 3 - GABINETE 5</t>
         </is>
       </c>
       <c r="E206" s="3" t="n">
@@ -2369,7 +2369,7 @@
     <row r="207" ht="15.75" customHeight="1" s="4">
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - SALA DOS PROFESSORES 3 - GABINETE 6</t>
+          <t>DMAFE - SALA DOS PROFESSORES 3 - GABINETE 6</t>
         </is>
       </c>
       <c r="E207" s="3" t="n">
@@ -2409,7 +2409,7 @@
     <row r="211" ht="15.75" customHeight="1" s="4">
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>DEMAFE - IPCA - LAB PESQUISA ENS DE MAT - LAPEM</t>
+          <t>DMAFE - IPCA - LAB PESQUISA ENS DE MAT - LAPEM</t>
         </is>
       </c>
       <c r="E211" s="3" t="n">
@@ -2486,7 +2486,7 @@
     <row r="219" ht="15.75" customHeight="1" s="4">
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA DE PROFESSORES E REUNIÃO</t>
+          <t>DZO - SALA 7</t>
         </is>
       </c>
       <c r="E219" s="3" t="n">
@@ -2496,7 +2496,7 @@
     <row r="220" ht="15.75" customHeight="1" s="4">
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 6</t>
+          <t>DZO - SALA 8</t>
         </is>
       </c>
       <c r="E220" s="3" t="n">
@@ -2506,7 +2506,7 @@
     <row r="221" ht="15.75" customHeight="1" s="4">
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>DZO - SALA 7</t>
+          <t>DZO - SALA 9</t>
         </is>
       </c>
       <c r="E221" s="3" t="n">
@@ -2900,7 +2900,7 @@
     <row r="261" ht="15.75" customHeight="1" s="4">
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>NEFI - NUCLEO DE EDUCACAO FISICA</t>
+          <t>EFI - NUCLEO DE EDUCACAO FISICA</t>
         </is>
       </c>
       <c r="E261" s="3" t="n">

--- a/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
+++ b/CODIGOS_CENTRO_DE_CUSTO_SISERGE_2025_CORRIGIDA.xlsx
@@ -656,14 +656,14 @@
     <row r="30" ht="15.75" customHeight="1" s="4">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>COORDENACAO GERAL DE ASSUNTOS E REGISTROS ACADEMIC</t>
+          <t>COORD. GERAL DE REGISTROS ACADÊMICOS</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="4">
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>COORDENACAO GERAL DE ASSUNTOS E REGISTROS ACADEMIC</t>
+          <t>COORD. GERAL DE REGISTROS ACADÊMICOS</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -1252,7 +1252,7 @@
     <row r="92" ht="15.75" customHeight="1" s="4">
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>DAAA - AGRICULTURA - SALA PROFESSORES (AO LADO DA SALA 4)</t>
+          <t>DAAA - AGRICULTURA - SALA PROFESSOR (SALA4)</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
@@ -2593,7 +2593,7 @@
     <row r="230" ht="15.75" customHeight="1" s="4">
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>DZO - PREDIO DA ZOOTECNIA - SALA 9</t>
+          <t>DZO - PREDIO DA ZOOTECNIA - COZ / SALA / DEPOSITO</t>
         </is>
       </c>
       <c r="E230" s="3" t="n">
@@ -3319,7 +3319,7 @@
     <row r="305" ht="15.75" customHeight="1" s="4">
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>PATRIMONIO - GALPAO 2 - IRRECUPERÁVEL</t>
+          <t>GALPAO 2 - IRRECUPERAVEL/ANTIECONOMICO</t>
         </is>
       </c>
       <c r="E305" s="3" t="n">
